--- a/output/yearly_surface_area_iteration_80_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_80_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497641144826</v>
+        <v>10.84497636042757</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907221799577</v>
+        <v>37.78907204021534</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.086434855702724</v>
+        <v>4.700608007933728</v>
       </c>
       <c r="C2" t="n">
-        <v>11.45405046544754</v>
+        <v>14.31486327562274</v>
       </c>
       <c r="D2" t="n">
-        <v>25.083653843506</v>
+        <v>27.73829963578938</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.71916340332318</v>
+        <v>15.64905840569416</v>
       </c>
       <c r="C3" t="n">
-        <v>26.35501712050563</v>
+        <v>42.06298038845459</v>
       </c>
       <c r="D3" t="n">
-        <v>77.48443755767951</v>
+        <v>78.0293075335365</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.14853130744431</v>
+        <v>30.69434197327653</v>
       </c>
       <c r="C4" t="n">
-        <v>101.5274388346839</v>
+        <v>92.68287376712438</v>
       </c>
       <c r="D4" t="n">
-        <v>84.14461398328987</v>
+        <v>104.1693219068121</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.12955930589413</v>
+        <v>40.25165587411923</v>
       </c>
       <c r="C5" t="n">
-        <v>172.542159021377</v>
+        <v>138.7700379952867</v>
       </c>
       <c r="D5" t="n">
-        <v>53.4070751110265</v>
+        <v>78.09802987283378</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.62650357069227</v>
+        <v>39.64788103600744</v>
       </c>
       <c r="C6" t="n">
-        <v>171.7135639589926</v>
+        <v>140.1562657536832</v>
       </c>
       <c r="D6" t="n">
-        <v>39.88939097125216</v>
+        <v>51.11960296013142</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.54217107911827</v>
+        <v>28.7455727803466</v>
       </c>
       <c r="C7" t="n">
-        <v>129.9539436111503</v>
+        <v>116.4794563703628</v>
       </c>
       <c r="D7" t="n">
-        <v>36.9500383447372</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.85522542358599</v>
+        <v>14.93729132011522</v>
       </c>
       <c r="C8" t="n">
-        <v>74.93680226515903</v>
+        <v>77.18991324640547</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>39.04999668412111</v>
+        <v>42.93280885441725</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.666614269321427</v>
+        <v>7.658166849730542</v>
       </c>
       <c r="C21" t="n">
-        <v>93.91602479918748</v>
+        <v>92.85527305298281</v>
       </c>
       <c r="D21" t="n">
-        <v>8.624941052986605</v>
+        <v>7.658166849730542</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.186393195086652</v>
+        <v>5.443791020048564</v>
       </c>
       <c r="C2" t="n">
-        <v>12.74701219194058</v>
+        <v>9.445394662558563</v>
       </c>
       <c r="D2" t="n">
-        <v>21.32748712705771</v>
+        <v>27.95133888761094</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.6209886328985</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="C3" t="n">
-        <v>34.94040079414398</v>
+        <v>48.47870163570749</v>
       </c>
       <c r="D3" t="n">
-        <v>78.53490760122361</v>
+        <v>80.67511759648164</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.00439432136928</v>
+        <v>30.06896868567131</v>
       </c>
       <c r="C4" t="n">
-        <v>83.54476613599506</v>
+        <v>98.43886055712343</v>
       </c>
       <c r="D4" t="n">
-        <v>98.79621672146926</v>
+        <v>115.1580239604466</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.56567627075797</v>
+        <v>42.53421928649306</v>
       </c>
       <c r="C5" t="n">
-        <v>178.9726064841936</v>
+        <v>151.9745446174063</v>
       </c>
       <c r="D5" t="n">
-        <v>68.4278149860027</v>
+        <v>94.49321653375551</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.91205328390785</v>
+        <v>46.00764266411829</v>
       </c>
       <c r="C6" t="n">
-        <v>215.4268622382861</v>
+        <v>176.5840143197611</v>
       </c>
       <c r="D6" t="n">
-        <v>45.80638438474769</v>
+        <v>61.02151030516475</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.70482240285375</v>
+        <v>36.83026512481909</v>
       </c>
       <c r="C7" t="n">
-        <v>181.516314785897</v>
+        <v>154.0283608146906</v>
       </c>
       <c r="D7" t="n">
-        <v>39.82459562277186</v>
+        <v>44.55563780953724</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.11524969649115</v>
+        <v>22.19731559302038</v>
       </c>
       <c r="C8" t="n">
-        <v>118.580396457451</v>
+        <v>112.1548577331556</v>
       </c>
       <c r="D8" t="n">
-        <v>37.38495257771854</v>
+        <v>37.80219535202343</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.20468654856884</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>62.34686970589792</v>
+        <v>65.78593191387449</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>37.72365553568369</v>
+        <v>39.57424995818893</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>31.62994753542373</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
         <v>34.93156506480576</v>
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1287,7 +1287,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
         <v>20.25247339090745</v>
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.835338634004855</v>
+        <v>7.828307660441181</v>
       </c>
       <c r="C21" t="n">
-        <v>101.8594022420631</v>
+        <v>100.7894611281802</v>
       </c>
       <c r="D21" t="n">
-        <v>9.79417329250607</v>
+        <v>8.806846117996329</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.068984381204535</v>
+        <v>6.584581852383357</v>
       </c>
       <c r="C2" t="n">
-        <v>11.4805576534622</v>
+        <v>15.40754847044944</v>
       </c>
       <c r="D2" t="n">
-        <v>23.94384475887546</v>
+        <v>25.11114277922492</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.55150553007523</v>
+        <v>16.29701189049705</v>
       </c>
       <c r="C3" t="n">
-        <v>41.04196277603791</v>
+        <v>42.76983873551229</v>
       </c>
       <c r="D3" t="n">
-        <v>76.88066271956772</v>
+        <v>82.5993430968054</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.43457974227862</v>
+        <v>29.02242563294421</v>
       </c>
       <c r="C4" t="n">
-        <v>84.80827543136071</v>
+        <v>106.8367304192506</v>
       </c>
       <c r="D4" t="n">
-        <v>110.959089029383</v>
+        <v>125.278861043527</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.81111319681967</v>
+        <v>43.56505437595222</v>
       </c>
       <c r="C5" t="n">
-        <v>166.3080610994097</v>
+        <v>163.8536918387927</v>
       </c>
       <c r="D5" t="n">
-        <v>82.02502068982102</v>
+        <v>107.7713542336936</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.14476854754334</v>
+        <v>50.15356321915257</v>
       </c>
       <c r="C6" t="n">
-        <v>241.4696835888413</v>
+        <v>201.2582793705962</v>
       </c>
       <c r="D6" t="n">
-        <v>54.09822549481625</v>
+        <v>72.81524547628169</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.25053525769474</v>
+        <v>43.71722527011047</v>
       </c>
       <c r="C7" t="n">
-        <v>234.5159645996611</v>
+        <v>193.9727296573805</v>
       </c>
       <c r="D7" t="n">
-        <v>42.57937968088841</v>
+        <v>49.52622643613884</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.79251674370121</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="C8" t="n">
-        <v>166.062624173348</v>
+        <v>150.207398749762</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.47254910757476</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.8640611529242</v>
+        <v>15.19843620944487</v>
       </c>
       <c r="C9" t="n">
-        <v>95.29530440812512</v>
+        <v>94.407804483486</v>
       </c>
       <c r="D9" t="n">
-        <v>36.49843440078366</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="C10" t="n">
-        <v>51.81664383014665</v>
+        <v>54.52135875534661</v>
       </c>
       <c r="D10" t="n">
         <v>35.87306111317846</v>
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.49392657288993</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1545,10 +1545,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.39843500367074</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
         <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1598,7 +1598,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
         <v>21.49242074137117</v>
@@ -1612,7 +1612,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
         <v>19.36104647545135</v>
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.987117066008025</v>
+        <v>7.981346911217286</v>
       </c>
       <c r="C21" t="n">
-        <v>108.8244700243593</v>
+        <v>107.7481833014334</v>
       </c>
       <c r="D21" t="n">
-        <v>10.98228596576103</v>
+        <v>9.976683639021607</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.395505456091222</v>
+        <v>6.051492848977339</v>
       </c>
       <c r="C2" t="n">
-        <v>8.081747101359742</v>
+        <v>10.84634863651876</v>
       </c>
       <c r="D2" t="n">
-        <v>20.04041588679014</v>
+        <v>20.88177366932965</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.29058162492383</v>
+        <v>19.50732688338412</v>
       </c>
       <c r="C3" t="n">
-        <v>58.99812828671207</v>
+        <v>66.20415643588366</v>
       </c>
       <c r="D3" t="n">
-        <v>82.89386740807943</v>
+        <v>90.59076940937443</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.96013355922015</v>
+        <v>20.930861054542</v>
       </c>
       <c r="C4" t="n">
-        <v>127.7931169141031</v>
+        <v>138.194733840598</v>
       </c>
       <c r="D4" t="n">
-        <v>101.2594217114245</v>
+        <v>119.8419422574081</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.04777114680538</v>
+        <v>28.24979018970198</v>
       </c>
       <c r="C5" t="n">
-        <v>144.292368831675</v>
+        <v>120.2640937702343</v>
       </c>
       <c r="D5" t="n">
-        <v>53.57888095926969</v>
+        <v>71.42214548395546</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.34345713223292</v>
+        <v>27.12961605915636</v>
       </c>
       <c r="C6" t="n">
-        <v>154.4456035889955</v>
+        <v>127.7587557444544</v>
       </c>
       <c r="D6" t="n">
-        <v>28.01515248838698</v>
+        <v>32.60384125803657</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.36144738607885</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="C7" t="n">
-        <v>116.7788894201581</v>
+        <v>105.6399799677738</v>
       </c>
       <c r="D7" t="n">
-        <v>27.60772719112455</v>
+        <v>28.44613973055133</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.01520924164921</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>70.18023463808323</v>
+        <v>69.5126461991954</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8704346652352</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>39.49374664644068</v>
+        <v>41.60155896745857</v>
       </c>
       <c r="D9" t="n">
         <v>27.29062268265283</v>
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>28.61303684027329</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
         <v>28.61303684027329</v>
@@ -1842,10 +1842,10 @@
         <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6145740628585034</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
         <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1895,7 +1895,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
         <v>17.91689560250429</v>
@@ -1909,7 +1909,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
         <v>16.53263133951629</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.449280595646544</v>
+        <v>3.712969817461437</v>
       </c>
       <c r="C2" t="n">
-        <v>5.282784396552087</v>
+        <v>4.856705892908971</v>
       </c>
       <c r="D2" t="n">
-        <v>13.84656962069701</v>
+        <v>14.25792190877643</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.45042657426681</v>
+        <v>20.57252314249191</v>
       </c>
       <c r="C3" t="n">
-        <v>46.42194019531043</v>
+        <v>55.57673753741193</v>
       </c>
       <c r="D3" t="n">
-        <v>80.46404184006859</v>
+        <v>87.28227964606268</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.86025733529424</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="C4" t="n">
-        <v>140.1091418638793</v>
+        <v>154.2757612361608</v>
       </c>
       <c r="D4" t="n">
-        <v>116.5746858976748</v>
+        <v>135.1572064436584</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.89483948912113</v>
+        <v>30.85142160595602</v>
       </c>
       <c r="C5" t="n">
-        <v>188.1519475189012</v>
+        <v>180.7888397370502</v>
       </c>
       <c r="D5" t="n">
-        <v>69.23775684200632</v>
+        <v>88.92179831215486</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.37491411649783</v>
+        <v>31.71830482880595</v>
       </c>
       <c r="C6" t="n">
-        <v>189.2230342642345</v>
+        <v>157.0217095649391</v>
       </c>
       <c r="D6" t="n">
-        <v>33.65038431076368</v>
+        <v>40.45291415348983</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.92416874706152</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="C7" t="n">
-        <v>155.8249591134622</v>
+        <v>136.4216974867282</v>
       </c>
       <c r="D7" t="n">
-        <v>30.00319158948677</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>93.87962421860124</v>
+        <v>91.12582190818894</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>43.59843379789659</v>
+        <v>45.5953086283346</v>
       </c>
       <c r="D9" t="n">
         <v>28.51093507903161</v>
@@ -2139,10 +2139,10 @@
         <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.46715734296802</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
         <v>29.31989518733098</v>
@@ -2170,7 +2170,7 @@
         <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
         <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2192,7 +2192,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
         <v>15.05706454003333</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.348160582109124</v>
+        <v>3.316343744945725</v>
       </c>
       <c r="C2" t="n">
-        <v>11.50902833688536</v>
+        <v>9.515098749560087</v>
       </c>
       <c r="D2" t="n">
-        <v>12.67632635723482</v>
+        <v>16.66811252270235</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.00310947402876</v>
+        <v>16.77806826557799</v>
       </c>
       <c r="C3" t="n">
-        <v>33.07998889459628</v>
+        <v>36.72718161587317</v>
       </c>
       <c r="D3" t="n">
-        <v>74.29866625739861</v>
+        <v>80.07625149689109</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.6755498981756</v>
+        <v>32.78742807873073</v>
       </c>
       <c r="C4" t="n">
-        <v>128.0611340373625</v>
+        <v>146.4649765011731</v>
       </c>
       <c r="D4" t="n">
-        <v>126.133963293926</v>
+        <v>143.8358561492002</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.3680829402971</v>
+        <v>35.76016012719008</v>
       </c>
       <c r="C5" t="n">
-        <v>222.709466708389</v>
+        <v>231.0543221944869</v>
       </c>
       <c r="D5" t="n">
-        <v>90.90983741325465</v>
+        <v>112.4591995214722</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.36611944488861</v>
+        <v>36.10573531908495</v>
       </c>
       <c r="C6" t="n">
-        <v>237.8872862160447</v>
+        <v>214.4608224973073</v>
       </c>
       <c r="D6" t="n">
-        <v>44.67933802027235</v>
+        <v>55.06426523579511</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.36818075128833</v>
+        <v>25.51169584255761</v>
       </c>
       <c r="C7" t="n">
-        <v>209.0042687571035</v>
+        <v>177.6835717485175</v>
       </c>
       <c r="D7" t="n">
-        <v>32.39865598784899</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.01797455831271</v>
+        <v>12.35038611942487</v>
       </c>
       <c r="C8" t="n">
-        <v>141.8625432636641</v>
+        <v>129.7625028088221</v>
       </c>
       <c r="D8" t="n">
-        <v>29.12354564648163</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>72.55311883924776</v>
+        <v>72.66405632982764</v>
       </c>
       <c r="D9" t="n">
         <v>29.06562253193106</v>
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>39.71660337530471</v>
+        <v>40.9977841293468</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
         <v>29.852984190737</v>
@@ -2481,7 +2481,7 @@
         <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.632065595085698</v>
+        <v>2.037126486312132</v>
       </c>
       <c r="C2" t="n">
-        <v>5.646031047123406</v>
+        <v>4.656429361242622</v>
       </c>
       <c r="D2" t="n">
-        <v>8.946666828801183</v>
+        <v>11.774100217032</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.86075605691298</v>
+        <v>16.16938468894497</v>
       </c>
       <c r="C3" t="n">
-        <v>39.86386553094174</v>
+        <v>39.1668246609265</v>
       </c>
       <c r="D3" t="n">
-        <v>71.70194357966579</v>
+        <v>78.7214396650305</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.13424706023711</v>
+        <v>35.79943003535994</v>
       </c>
       <c r="C4" t="n">
-        <v>125.1639965621301</v>
+        <v>142.3043297305751</v>
       </c>
       <c r="D4" t="n">
-        <v>134.4042059545011</v>
+        <v>152.4251668136555</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.23340357836604</v>
+        <v>37.5518496874405</v>
       </c>
       <c r="C5" t="n">
-        <v>263.6728896680871</v>
+        <v>276.7792215197821</v>
       </c>
       <c r="D5" t="n">
-        <v>93.38875036647785</v>
+        <v>115.0608309377262</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.24157635516951</v>
+        <v>29.82647700272235</v>
       </c>
       <c r="C6" t="n">
-        <v>273.1477367617731</v>
+        <v>245.2130875851344</v>
       </c>
       <c r="D6" t="n">
-        <v>44.07556318216056</v>
+        <v>53.41394734495622</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.144578954431539</v>
       </c>
       <c r="C7" t="n">
-        <v>203.9139069105838</v>
+        <v>177.9231181883537</v>
       </c>
       <c r="D7" t="n">
-        <v>32.45854259780804</v>
+        <v>34.19525428662065</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>93.79617566374026</v>
+        <v>90.37478491444013</v>
       </c>
       <c r="D8" t="n">
-        <v>31.12631096314512</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>30.28593492830985</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
         <v>23.34596040698915</v>
@@ -2778,7 +2778,7 @@
         <v>19.19120412261664</v>
       </c>
       <c r="D11" t="n">
-        <v>22.7451308119901</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.633448253417445</v>
+        <v>2.036144738607885</v>
       </c>
       <c r="C2" t="n">
-        <v>7.064656479760047</v>
+        <v>5.779548734900973</v>
       </c>
       <c r="D2" t="n">
-        <v>12.25613833981718</v>
+        <v>11.75152001983432</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.76548547187203</v>
+        <v>11.85460352878024</v>
       </c>
       <c r="C3" t="n">
-        <v>31.12140222462389</v>
+        <v>29.05482330718435</v>
       </c>
       <c r="D3" t="n">
-        <v>63.5436201573748</v>
+        <v>71.77066591896308</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.39851711912875</v>
+        <v>33.68081848959532</v>
       </c>
       <c r="C4" t="n">
-        <v>114.0476673069435</v>
+        <v>121.4628077171196</v>
       </c>
       <c r="D4" t="n">
-        <v>138.2968356018397</v>
+        <v>155.3095415687327</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.57825906446394</v>
+        <v>43.98229715025711</v>
       </c>
       <c r="C5" t="n">
-        <v>251.0083442833033</v>
+        <v>272.3613568506714</v>
       </c>
       <c r="D5" t="n">
-        <v>115.2080930933632</v>
+        <v>135.4811831860599</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.05668899160162</v>
+        <v>37.15227837181205</v>
       </c>
       <c r="C6" t="n">
-        <v>336.1415782047697</v>
+        <v>327.6484788153306</v>
       </c>
       <c r="D6" t="n">
-        <v>57.11709968537519</v>
+        <v>69.59511300635215</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.48689010804419</v>
+        <v>16.28915790886308</v>
       </c>
       <c r="C7" t="n">
-        <v>281.2275203677243</v>
+        <v>250.9248957284423</v>
       </c>
       <c r="D7" t="n">
-        <v>36.29128563518759</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>161.7232993205771</v>
+        <v>144.5328970192154</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.62838495064274</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>58.57499502618167</v>
+        <v>58.242182554442</v>
       </c>
       <c r="D9" t="n">
         <v>32.39374724932775</v>
@@ -3072,7 +3072,7 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
         <v>24.20008090968388</v>
@@ -3089,7 +3089,7 @@
         <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
         <v>15.60978849752428</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.13520344574558</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>24.38563122578652</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.339504779220149</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C2" t="n">
-        <v>4.018293353482195</v>
+        <v>3.692353115672254</v>
       </c>
       <c r="D2" t="n">
-        <v>9.460120878122265</v>
+        <v>10.04327901444487</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.85246010692249</v>
+        <v>9.954921721062657</v>
       </c>
       <c r="C3" t="n">
-        <v>30.09056713516474</v>
+        <v>26.72317250959818</v>
       </c>
       <c r="D3" t="n">
-        <v>59.93078860574654</v>
+        <v>66.52322443976388</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.00363355784328</v>
+        <v>30.29869764846506</v>
       </c>
       <c r="C4" t="n">
-        <v>101.4508625137527</v>
+        <v>105.2413903998496</v>
       </c>
       <c r="D4" t="n">
-        <v>138.7690562475824</v>
+        <v>157.4664412749629</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.11884219660543</v>
+        <v>47.59021996336414</v>
       </c>
       <c r="C5" t="n">
-        <v>244.7742463613361</v>
+        <v>261.8812001078367</v>
       </c>
       <c r="D5" t="n">
-        <v>129.8361338866407</v>
+        <v>148.3175344190869</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.53091419048183</v>
+        <v>41.98247707670636</v>
       </c>
       <c r="C6" t="n">
-        <v>371.5227837181205</v>
+        <v>374.7831678439242</v>
       </c>
       <c r="D6" t="n">
-        <v>67.66303352439442</v>
+        <v>81.8316163920844</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.51063197939536</v>
+        <v>14.49255961009142</v>
       </c>
       <c r="C7" t="n">
-        <v>347.5818842023577</v>
+        <v>319.0159712518883</v>
       </c>
       <c r="D7" t="n">
-        <v>40.60312155223958</v>
+        <v>44.6155244194963</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>208.2041443781423</v>
+        <v>186.3406230045658</v>
       </c>
       <c r="D8" t="n">
-        <v>32.54493639578176</v>
+        <v>33.04562772494764</v>
       </c>
     </row>
     <row r="9">
@@ -3369,7 +3369,7 @@
         <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>62.90155715879737</v>
+        <v>62.23593221531803</v>
       </c>
       <c r="D9" t="n">
         <v>32.06093477758807</v>
@@ -3383,7 +3383,7 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
         <v>24.76949457814703</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.85664913964673</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
         <v>19.7439280801076</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.906954952274805</v>
+        <v>2.431789063419349</v>
       </c>
       <c r="C2" t="n">
-        <v>6.206608986248336</v>
+        <v>6.603235058764047</v>
       </c>
       <c r="D2" t="n">
-        <v>11.33133200241669</v>
+        <v>20.11011997379167</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.08884031946772</v>
+        <v>7.628179661997716</v>
       </c>
       <c r="C3" t="n">
-        <v>23.63066724122073</v>
+        <v>21.1910241961674</v>
       </c>
       <c r="D3" t="n">
-        <v>54.77170441992956</v>
+        <v>60.54438092090079</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.28142710041612</v>
+        <v>25.07874510498477</v>
       </c>
       <c r="C4" t="n">
-        <v>90.19414333685872</v>
+        <v>88.96892220195869</v>
       </c>
       <c r="D4" t="n">
-        <v>136.8418855041459</v>
+        <v>154.7607446020587</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.77523050011905</v>
+        <v>47.02571503342222</v>
       </c>
       <c r="C5" t="n">
-        <v>221.0650393037756</v>
+        <v>234.1468274628643</v>
       </c>
       <c r="D5" t="n">
-        <v>142.9670094309418</v>
+        <v>163.0682936753952</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.58753676215866</v>
+        <v>48.86551023118075</v>
       </c>
       <c r="C6" t="n">
-        <v>379.2108499900773</v>
+        <v>391.2863467523131</v>
       </c>
       <c r="D6" t="n">
-        <v>82.8781594448115</v>
+        <v>99.38133835320039</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.60772719112455</v>
+        <v>25.27214940272139</v>
       </c>
       <c r="C7" t="n">
-        <v>417.7689910743707</v>
+        <v>400.7013072360399</v>
       </c>
       <c r="D7" t="n">
-        <v>47.25053525769474</v>
+        <v>51.98157744446011</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>7.260024272905162</v>
       </c>
       <c r="C8" t="n">
-        <v>297.4106495245288</v>
+        <v>271.5415975176253</v>
       </c>
       <c r="D8" t="n">
-        <v>34.79804737702819</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>128.4656140915121</v>
+        <v>116.7062400900438</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>44.12955930589413</v>
+        <v>43.98720588877834</v>
       </c>
       <c r="D10" t="n">
         <v>25.76596849795754</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.314601233715485</v>
+        <v>6.079963532400496</v>
       </c>
       <c r="C2" t="n">
-        <v>5.788384464239194</v>
+        <v>7.530004891573035</v>
       </c>
       <c r="D2" t="n">
-        <v>3.05029011709484</v>
+        <v>10.51549966018759</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.148063976892021</v>
+        <v>1.795616551067416</v>
       </c>
       <c r="C2" t="n">
-        <v>3.723769042208152</v>
+        <v>3.962333734340127</v>
       </c>
       <c r="D2" t="n">
-        <v>8.430267536367362</v>
+        <v>15.12185988851362</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.47586989911922</v>
+        <v>10.56360529769568</v>
       </c>
       <c r="C3" t="n">
-        <v>27.96999209399163</v>
+        <v>26.1783025337412</v>
       </c>
       <c r="D3" t="n">
-        <v>59.79334392715199</v>
+        <v>67.51969835957439</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.82343394861837</v>
+        <v>35.40378571054848</v>
       </c>
       <c r="C4" t="n">
-        <v>127.6016761117749</v>
+        <v>129.4777959745906</v>
       </c>
       <c r="D4" t="n">
-        <v>139.4071922553428</v>
+        <v>157.8493228796191</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.31775176547326</v>
+        <v>27.51347941151687</v>
       </c>
       <c r="C5" t="n">
-        <v>326.0138688877596</v>
+        <v>337.9175598017522</v>
       </c>
       <c r="D5" t="n">
-        <v>126.8172596960817</v>
+        <v>146.1086020845316</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.10695374650067</v>
+        <v>15.65789413503238</v>
       </c>
       <c r="C6" t="n">
-        <v>338.3554192778463</v>
+        <v>329.0975384267988</v>
       </c>
       <c r="D6" t="n">
-        <v>67.18001365390501</v>
+        <v>77.8467024605466</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>4.790928796724434</v>
       </c>
       <c r="C7" t="n">
-        <v>209.1240419770216</v>
+        <v>190.9185125494687</v>
       </c>
       <c r="D7" t="n">
-        <v>30.00319158948677</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>94.63066121235005</v>
+        <v>85.95201150680825</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>24.45042657426681</v>
       </c>
     </row>
     <row r="9">
@@ -4302,7 +4302,7 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>33.61405964570653</v>
+        <v>33.50312215512664</v>
       </c>
       <c r="D9" t="n">
         <v>19.63593583264045</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.35653864755762</v>
+        <v>20.4988920646734</v>
       </c>
       <c r="D10" t="n">
-        <v>18.79065105928395</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.9264920953685</v>
+        <v>14.74879576089983</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>15.99267010218054</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
         <v>13.0179745583127</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
         <v>9.105709956889166</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>18.12993485432585</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.533931882390022</v>
+        <v>6.630723994482958</v>
       </c>
       <c r="C2" t="n">
-        <v>8.464628706015999</v>
+        <v>8.009097771245479</v>
       </c>
       <c r="D2" t="n">
-        <v>9.439504176333081</v>
+        <v>22.01078352921349</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.41067364001143</v>
+        <v>12.91489104936679</v>
       </c>
       <c r="C3" t="n">
-        <v>14.81457285708437</v>
+        <v>18.97227438456961</v>
       </c>
       <c r="D3" t="n">
-        <v>5.821763886183586</v>
+        <v>11.96750451476862</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39940282942036</v>
+        <v>13.39786025085413</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14981481284775</v>
+        <v>70.14173896035399</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576400332872983</v>
+        <v>1.576218853041663</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.976479112827081</v>
+        <v>4.500331476267379</v>
       </c>
       <c r="C2" t="n">
-        <v>8.376271412633786</v>
+        <v>5.471279955767474</v>
       </c>
       <c r="D2" t="n">
-        <v>16.6357148484622</v>
+        <v>30.39785416659399</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.96522222419064</v>
+        <v>18.91827826083604</v>
       </c>
       <c r="C3" t="n">
-        <v>26.3942870286755</v>
+        <v>26.64463269325843</v>
       </c>
       <c r="D3" t="n">
-        <v>12.34056864238241</v>
+        <v>27.5625667967292</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.57051858935441</v>
+        <v>15.02172162268045</v>
       </c>
       <c r="C4" t="n">
-        <v>23.4834050855837</v>
+        <v>29.46912083837651</v>
       </c>
       <c r="D4" t="n">
-        <v>18.12306262039612</v>
+        <v>21.33926809950867</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4445352185235</v>
+        <v>15.43877004918423</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16424911386794</v>
+        <v>86.13208553755412</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251481098636526</v>
+        <v>3.250267378775627</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.838052686528282</v>
+        <v>5.239587497565227</v>
       </c>
       <c r="C2" t="n">
-        <v>11.28911685113407</v>
+        <v>6.735770998837365</v>
       </c>
       <c r="D2" t="n">
-        <v>21.88119283225291</v>
+        <v>30.56867826713293</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.85937339858123</v>
+        <v>17.03823140720339</v>
       </c>
       <c r="C3" t="n">
-        <v>30.15438073594078</v>
+        <v>23.43431770037137</v>
       </c>
       <c r="D3" t="n">
-        <v>22.78145547704723</v>
+        <v>45.48437113775472</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.64779892054943</v>
+        <v>27.31222113214627</v>
       </c>
       <c r="C4" t="n">
-        <v>48.56215019056847</v>
+        <v>50.73181261695392</v>
       </c>
       <c r="D4" t="n">
-        <v>20.24167416616074</v>
+        <v>30.3497485290859</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.76901155206152</v>
+        <v>13.08178815908875</v>
       </c>
       <c r="C5" t="n">
-        <v>26.97351817418112</v>
+        <v>33.35487825178539</v>
       </c>
       <c r="D5" t="n">
-        <v>28.98610096788708</v>
+        <v>30.33600406122645</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5288,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
         <v>30.17892442854696</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73992150308528</v>
+        <v>16.72755501600167</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1135211688202</v>
+        <v>102.0380855976102</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021976450925584</v>
+        <v>4.181888754000417</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.970588626601601</v>
+        <v>4.799764526062656</v>
       </c>
       <c r="C2" t="n">
-        <v>12.96594192998763</v>
+        <v>12.99637610881928</v>
       </c>
       <c r="D2" t="n">
-        <v>23.45297090675205</v>
+        <v>24.81072798172539</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.60764507566654</v>
+        <v>17.47510913559323</v>
       </c>
       <c r="C3" t="n">
-        <v>38.02308858547897</v>
+        <v>24.94130042639022</v>
       </c>
       <c r="D3" t="n">
-        <v>34.34153469455343</v>
+        <v>58.60052046649211</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.52766584773282</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="C4" t="n">
-        <v>63.58387181324892</v>
+        <v>54.57339138367169</v>
       </c>
       <c r="D4" t="n">
-        <v>26.73789872516188</v>
+        <v>45.4608091928528</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.96155727528091</v>
+        <v>27.02260555939346</v>
       </c>
       <c r="C5" t="n">
-        <v>60.57383335202821</v>
+        <v>65.92435834017333</v>
       </c>
       <c r="D5" t="n">
-        <v>29.52606220522283</v>
+        <v>33.94392687433348</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.31700669748049</v>
+        <v>11.7132318593687</v>
       </c>
       <c r="C6" t="n">
-        <v>28.33716573537994</v>
+        <v>33.2881194078966</v>
       </c>
       <c r="D6" t="n">
-        <v>37.99756314516856</v>
+        <v>38.31957639216151</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
         <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5613,10 +5613,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06555652072663</v>
+        <v>18.04571873040065</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8562496828357</v>
+        <v>117.7268317173757</v>
       </c>
       <c r="D21" t="n">
-        <v>6.882116769800623</v>
+        <v>6.015239576800216</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.760314691443536</v>
+        <v>5.229770020522759</v>
       </c>
       <c r="C2" t="n">
-        <v>14.23141472076176</v>
+        <v>10.60483870127405</v>
       </c>
       <c r="D2" t="n">
-        <v>32.4408711391316</v>
+        <v>25.47831642061323</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.37416904850505</v>
+        <v>14.96183501272139</v>
       </c>
       <c r="C3" t="n">
-        <v>42.3673221767711</v>
+        <v>36.8891699870739</v>
       </c>
       <c r="D3" t="n">
-        <v>41.88626580169017</v>
+        <v>60.61310326019807</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.65757533986289</v>
+        <v>23.15157436154828</v>
       </c>
       <c r="C4" t="n">
-        <v>68.0125357071063</v>
+        <v>48.77911643320702</v>
       </c>
       <c r="D4" t="n">
-        <v>32.58322455624739</v>
+        <v>55.49230723484671</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.15099352447154</v>
+        <v>22.01569226773472</v>
       </c>
       <c r="C5" t="n">
-        <v>67.66696051521141</v>
+        <v>62.88094045700822</v>
       </c>
       <c r="D5" t="n">
-        <v>26.01631416254048</v>
+        <v>33.87029579651497</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.00757624419349</v>
+        <v>13.16229147083699</v>
       </c>
       <c r="C6" t="n">
-        <v>42.50574860306991</v>
+        <v>47.2956956520901</v>
       </c>
       <c r="D6" t="n">
-        <v>30.26924521733767</v>
+        <v>31.396291581813</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.868887775987432</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>20.12190094624263</v>
+        <v>22.0382724649324</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.059236341999063</v>
+        <v>7.049542824687475</v>
       </c>
       <c r="C21" t="n">
-        <v>67.06274524899109</v>
+        <v>66.08946398144506</v>
       </c>
       <c r="D21" t="n">
-        <v>5.294427256499297</v>
+        <v>4.405964265429671</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.183627878423159</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C2" t="n">
-        <v>7.39648720379547</v>
+        <v>10.04720600526186</v>
       </c>
       <c r="D2" t="n">
-        <v>35.549084370777</v>
+        <v>26.65150492718816</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.34672117051515</v>
+        <v>16.99405276051229</v>
       </c>
       <c r="C3" t="n">
-        <v>50.74653883251763</v>
+        <v>39.75587328347459</v>
       </c>
       <c r="D3" t="n">
-        <v>59.01285450227578</v>
+        <v>67.36752746541613</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.20561154301086</v>
+        <v>27.09525488950772</v>
       </c>
       <c r="C4" t="n">
-        <v>91.02372014694727</v>
+        <v>75.81055772193871</v>
       </c>
       <c r="D4" t="n">
-        <v>46.96681017116741</v>
+        <v>74.38113306455534</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.56318869153496</v>
+        <v>29.32971266437347</v>
       </c>
       <c r="C5" t="n">
-        <v>103.206227408946</v>
+        <v>78.76070957320037</v>
       </c>
       <c r="D5" t="n">
-        <v>32.00497515844602</v>
+        <v>46.48575379608648</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.75476836258333</v>
+        <v>22.78243722475149</v>
       </c>
       <c r="C6" t="n">
-        <v>80.74482168348318</v>
+        <v>78.32972233103602</v>
       </c>
       <c r="D6" t="n">
-        <v>32.20132469929539</v>
+        <v>35.58246379272141</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.97732199181109</v>
+        <v>11.31856928226148</v>
       </c>
       <c r="C7" t="n">
-        <v>44.19631814978291</v>
+        <v>48.98724694650735</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>23.53249247079604</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6255,7 +6255,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.277964941256789</v>
+        <v>7.2674545783539</v>
       </c>
       <c r="C21" t="n">
-        <v>76.41863188319628</v>
+        <v>75.39984125042172</v>
       </c>
       <c r="D21" t="n">
-        <v>6.36821932359969</v>
+        <v>5.450590933765425</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.268639018065131</v>
+        <v>4.549418861479719</v>
       </c>
       <c r="C2" t="n">
-        <v>4.296127953784042</v>
+        <v>11.2959890850638</v>
       </c>
       <c r="D2" t="n">
-        <v>27.91305072714531</v>
+        <v>28.95763028446392</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.96245690752714</v>
+        <v>16.01721379478671</v>
       </c>
       <c r="C3" t="n">
-        <v>37.8120128290659</v>
+        <v>39.31408681656352</v>
       </c>
       <c r="D3" t="n">
-        <v>72.90458451736815</v>
+        <v>72.6395126372215</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.59973434077034</v>
+        <v>30.52842661125882</v>
       </c>
       <c r="C4" t="n">
-        <v>111.507885996057</v>
+        <v>88.57327787714723</v>
       </c>
       <c r="D4" t="n">
-        <v>64.50278766442393</v>
+        <v>89.78573629189205</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.28186906877263</v>
+        <v>35.31837366027901</v>
       </c>
       <c r="C5" t="n">
-        <v>137.9846398318892</v>
+        <v>113.1464229144449</v>
       </c>
       <c r="D5" t="n">
-        <v>41.65064635267094</v>
+        <v>62.66004722355269</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.5359207399943</v>
+        <v>31.95981476405067</v>
       </c>
       <c r="C6" t="n">
-        <v>125.7059212948744</v>
+        <v>103.7687688434794</v>
       </c>
       <c r="D6" t="n">
-        <v>34.93843729873549</v>
+        <v>41.74096714146165</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.02020009562846</v>
+        <v>19.52303484665207</v>
       </c>
       <c r="C7" t="n">
-        <v>82.82318157337367</v>
+        <v>82.88306818333271</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>41.8911745402114</v>
+        <v>46.64774216728719</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>33.62976760897448</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>27.06874770149305</v>
+        <v>28.06718511671205</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.480539658385084</v>
+        <v>7.470905642054171</v>
       </c>
       <c r="C21" t="n">
-        <v>85.09113861413032</v>
+        <v>84.04768847310943</v>
       </c>
       <c r="D21" t="n">
-        <v>7.480539658385084</v>
+        <v>6.5370424367974</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_80_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_80_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497636042757</v>
+        <v>10.84497638338651</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907204021534</v>
+        <v>37.78907212021524</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.700608007933728</v>
+        <v>6.972372195560848</v>
       </c>
       <c r="C2" t="n">
-        <v>14.31486327562274</v>
+        <v>7.803912501057896</v>
       </c>
       <c r="D2" t="n">
-        <v>27.73829963578938</v>
+        <v>28.02104297461246</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.64905840569416</v>
+        <v>20.27309009269663</v>
       </c>
       <c r="C3" t="n">
-        <v>42.06298038845459</v>
+        <v>34.34644343307466</v>
       </c>
       <c r="D3" t="n">
-        <v>78.0293075335365</v>
+        <v>84.52847733565038</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.69434197327653</v>
+        <v>39.01563551447249</v>
       </c>
       <c r="C4" t="n">
-        <v>92.68287376712438</v>
+        <v>77.78877934599602</v>
       </c>
       <c r="D4" t="n">
-        <v>104.1693219068121</v>
+        <v>107.2068493037517</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.25165587411923</v>
+        <v>50.41274461307373</v>
       </c>
       <c r="C5" t="n">
-        <v>138.7700379952867</v>
+        <v>115.5271610972434</v>
       </c>
       <c r="D5" t="n">
-        <v>78.09802987283378</v>
+        <v>74.95643721924398</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.64788103600744</v>
+        <v>50.55607977789376</v>
       </c>
       <c r="C6" t="n">
-        <v>140.1562657536832</v>
+        <v>117.7763450876729</v>
       </c>
       <c r="D6" t="n">
-        <v>51.11960296013142</v>
+        <v>47.21519234034186</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.7455727803466</v>
+        <v>36.4110588551057</v>
       </c>
       <c r="C7" t="n">
-        <v>116.4794563703628</v>
+        <v>105.3405469179785</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>38.5669768136317</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.93729132011522</v>
+        <v>18.85937339858123</v>
       </c>
       <c r="C8" t="n">
-        <v>77.18991324640547</v>
+        <v>64.33883579781471</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>42.93280885441725</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.658166849730542</v>
+        <v>7.671834226611586</v>
       </c>
       <c r="C21" t="n">
-        <v>92.85527305298281</v>
+        <v>93.02098999766548</v>
       </c>
       <c r="D21" t="n">
-        <v>7.658166849730542</v>
+        <v>7.671834226611586</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.443791020048564</v>
+        <v>7.606581212504286</v>
       </c>
       <c r="C2" t="n">
-        <v>9.445394662558563</v>
+        <v>7.177557465748431</v>
       </c>
       <c r="D2" t="n">
-        <v>27.95133888761094</v>
+        <v>30.64819983117692</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.51652246562084</v>
+        <v>21.79479903427919</v>
       </c>
       <c r="C3" t="n">
-        <v>48.47870163570749</v>
+        <v>32.10805866739193</v>
       </c>
       <c r="D3" t="n">
-        <v>80.67511759648164</v>
+        <v>86.40361545076178</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.06896868567131</v>
+        <v>38.23710958500477</v>
       </c>
       <c r="C4" t="n">
-        <v>98.43886055712343</v>
+        <v>81.57930723209294</v>
       </c>
       <c r="D4" t="n">
-        <v>115.1580239604466</v>
+        <v>122.3179099675186</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.53421928649306</v>
+        <v>53.79977419272522</v>
       </c>
       <c r="C5" t="n">
-        <v>151.9745446174063</v>
+        <v>127.3817646260237</v>
       </c>
       <c r="D5" t="n">
-        <v>94.49321653375551</v>
+        <v>92.08793465835082</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.00764266411829</v>
+        <v>58.44540432922113</v>
       </c>
       <c r="C6" t="n">
-        <v>176.5840143197611</v>
+        <v>148.2871002402553</v>
       </c>
       <c r="D6" t="n">
-        <v>61.02151030516475</v>
+        <v>58.20389439397641</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.83026512481909</v>
+        <v>47.54996830749001</v>
       </c>
       <c r="C7" t="n">
-        <v>154.0283608146906</v>
+        <v>134.3855527481204</v>
       </c>
       <c r="D7" t="n">
-        <v>44.55563780953724</v>
+        <v>42.39971985101125</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.19731559302038</v>
+        <v>27.87181732356695</v>
       </c>
       <c r="C8" t="n">
-        <v>112.1548577331556</v>
+        <v>99.05343461998193</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>13.09062388842696</v>
       </c>
       <c r="C9" t="n">
-        <v>65.78593191387449</v>
+        <v>55.02499532762521</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>39.57424995818893</v>
+        <v>35.44600086183109</v>
       </c>
       <c r="D10" t="n">
         <v>35.16129402759952</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.828307660441181</v>
+        <v>7.846508389374458</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7894611281802</v>
+        <v>101.0237955131961</v>
       </c>
       <c r="D21" t="n">
-        <v>8.806846117996329</v>
+        <v>8.827321938046266</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.584581852383357</v>
+        <v>8.491135894030663</v>
       </c>
       <c r="C2" t="n">
-        <v>15.40754847044944</v>
+        <v>7.297330685666541</v>
       </c>
       <c r="D2" t="n">
-        <v>25.11114277922492</v>
+        <v>25.50973234714912</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.29701189049705</v>
+        <v>22.95326132529043</v>
       </c>
       <c r="C3" t="n">
-        <v>42.76983873551229</v>
+        <v>29.88930885579414</v>
       </c>
       <c r="D3" t="n">
-        <v>82.5993430968054</v>
+        <v>88.89234588102744</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.02242563294421</v>
+        <v>38.70933023074748</v>
       </c>
       <c r="C4" t="n">
-        <v>106.8367304192506</v>
+        <v>79.89462817160542</v>
       </c>
       <c r="D4" t="n">
-        <v>125.278861043527</v>
+        <v>132.1579672071844</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.56505437595222</v>
+        <v>55.34602682691395</v>
       </c>
       <c r="C5" t="n">
-        <v>163.8536918387927</v>
+        <v>136.9047173572177</v>
       </c>
       <c r="D5" t="n">
-        <v>107.7713542336936</v>
+        <v>109.8821117978243</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.15356321915257</v>
+        <v>63.87937787222722</v>
       </c>
       <c r="C6" t="n">
-        <v>201.2582793705962</v>
+        <v>169.3789679182937</v>
       </c>
       <c r="D6" t="n">
-        <v>72.81524547628169</v>
+        <v>69.31335141523331</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.71722527011047</v>
+        <v>56.35329997147116</v>
       </c>
       <c r="C7" t="n">
-        <v>193.9727296573805</v>
+        <v>166.7842087359694</v>
       </c>
       <c r="D7" t="n">
-        <v>49.52622643613884</v>
+        <v>48.02906118716245</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.04009709162065</v>
+        <v>37.30150402285756</v>
       </c>
       <c r="C8" t="n">
-        <v>150.207398749762</v>
+        <v>132.6832022289564</v>
       </c>
       <c r="D8" t="n">
-        <v>40.47254910757476</v>
+        <v>39.97185777840888</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.19843620944487</v>
+        <v>18.97031088916111</v>
       </c>
       <c r="C9" t="n">
-        <v>94.407804483486</v>
+        <v>82.20468051969816</v>
       </c>
       <c r="D9" t="n">
-        <v>36.38749691020377</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687084524252525</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>54.52135875534661</v>
+        <v>47.40368789955724</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>37.49392657288993</v>
+        <v>35.7169632282032</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>33.30088212805181</v>
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.981346911217286</v>
+        <v>8.004733532310823</v>
       </c>
       <c r="C21" t="n">
-        <v>107.7481833014334</v>
+        <v>108.0639026861961</v>
       </c>
       <c r="D21" t="n">
-        <v>9.976683639021607</v>
+        <v>10.00591691538853</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.051492848977339</v>
+        <v>7.858890372495717</v>
       </c>
       <c r="C2" t="n">
-        <v>10.84634863651876</v>
+        <v>5.019676011813941</v>
       </c>
       <c r="D2" t="n">
-        <v>20.88177366932965</v>
+        <v>21.26072828316892</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.50732688338412</v>
+        <v>26.95879195861741</v>
       </c>
       <c r="C3" t="n">
-        <v>66.20415643588366</v>
+        <v>45.75926049494383</v>
       </c>
       <c r="D3" t="n">
-        <v>90.59076940937443</v>
+        <v>96.68251391422589</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.930861054542</v>
+        <v>26.58474608329938</v>
       </c>
       <c r="C4" t="n">
-        <v>138.194733840598</v>
+        <v>111.2909197534184</v>
       </c>
       <c r="D4" t="n">
-        <v>119.8419422574081</v>
+        <v>125.7638444094249</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.24979018970198</v>
+        <v>35.9810533606456</v>
       </c>
       <c r="C5" t="n">
-        <v>120.2640937702343</v>
+        <v>101.19364461524</v>
       </c>
       <c r="D5" t="n">
-        <v>71.42214548395546</v>
+        <v>70.93127163183206</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.12961605915636</v>
+        <v>34.97868895460962</v>
       </c>
       <c r="C6" t="n">
-        <v>127.7587557444544</v>
+        <v>109.8467688804714</v>
       </c>
       <c r="D6" t="n">
-        <v>32.60384125803657</v>
+        <v>31.5975498611836</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.22360179685679</v>
+        <v>24.73316991308989</v>
       </c>
       <c r="C7" t="n">
-        <v>105.6399799677738</v>
+        <v>93.30333831620835</v>
       </c>
       <c r="D7" t="n">
-        <v>28.44613973055133</v>
+        <v>28.086820070797</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>13.18487166803466</v>
       </c>
       <c r="C8" t="n">
-        <v>69.5126461991954</v>
+        <v>60.58365082907067</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>41.60155896745857</v>
+        <v>36.16562192904399</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>27.90126975469435</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
         <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
         <v>27.12078032981814</v>
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.712969817461437</v>
+        <v>4.845906668162256</v>
       </c>
       <c r="C2" t="n">
-        <v>4.856705892908971</v>
+        <v>2.18831563276614</v>
       </c>
       <c r="D2" t="n">
-        <v>14.25792190877643</v>
+        <v>15.63433219013046</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.57252314249191</v>
+        <v>27.72946390645116</v>
       </c>
       <c r="C3" t="n">
-        <v>55.57673753741193</v>
+        <v>33.07998889459628</v>
       </c>
       <c r="D3" t="n">
-        <v>87.28227964606268</v>
+        <v>93.34948045830797</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.98864530037232</v>
+        <v>37.50963453615788</v>
       </c>
       <c r="C4" t="n">
-        <v>154.2757612361608</v>
+        <v>116.7788894201581</v>
       </c>
       <c r="D4" t="n">
-        <v>135.1572064436584</v>
+        <v>141.2322612375376</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.85142160595602</v>
+        <v>39.3680829402971</v>
       </c>
       <c r="C5" t="n">
-        <v>180.7888397370502</v>
+        <v>149.4220005863646</v>
       </c>
       <c r="D5" t="n">
-        <v>88.92179831215486</v>
+        <v>91.4497986505904</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.71830482880595</v>
+        <v>41.21769561509809</v>
       </c>
       <c r="C6" t="n">
-        <v>157.0217095649391</v>
+        <v>134.3197756519359</v>
       </c>
       <c r="D6" t="n">
-        <v>40.45291415348983</v>
+        <v>40.25165587411923</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.84620976779852</v>
+        <v>23.05634483423634</v>
       </c>
       <c r="C7" t="n">
-        <v>136.4216974867282</v>
+        <v>120.0127663579471</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>91.12582190818894</v>
+        <v>80.02716411167874</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>28.03871443328891</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>45.5953086283346</v>
+        <v>41.04687151455913</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>18.12993485432585</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.316343744945725</v>
+        <v>6.039711876526377</v>
       </c>
       <c r="C2" t="n">
-        <v>9.515098749560087</v>
+        <v>11.78489944177871</v>
       </c>
       <c r="D2" t="n">
-        <v>16.66811252270235</v>
+        <v>16.86544381125595</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.77806826557799</v>
+        <v>22.07950586851076</v>
       </c>
       <c r="C3" t="n">
-        <v>36.72718161587317</v>
+        <v>20.34181243199391</v>
       </c>
       <c r="D3" t="n">
-        <v>80.07625149689109</v>
+        <v>85.00953371073132</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.78742807873073</v>
+        <v>44.98858854711009</v>
       </c>
       <c r="C4" t="n">
-        <v>146.4649765011731</v>
+        <v>99.57474265093698</v>
       </c>
       <c r="D4" t="n">
-        <v>143.8358561492002</v>
+        <v>153.4972353066931</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.76016012719008</v>
+        <v>46.97662764820988</v>
       </c>
       <c r="C5" t="n">
-        <v>231.0543221944869</v>
+        <v>180.9361018926872</v>
       </c>
       <c r="D5" t="n">
-        <v>112.4591995214722</v>
+        <v>116.3371029532471</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.10573531908495</v>
+        <v>46.77242412572655</v>
       </c>
       <c r="C6" t="n">
-        <v>214.4608224973073</v>
+        <v>183.2255375389907</v>
       </c>
       <c r="D6" t="n">
-        <v>55.06426523579511</v>
+        <v>55.50703345041042</v>
       </c>
     </row>
     <row r="7">
@@ -2405,10 +2405,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.51169584255761</v>
+        <v>33.41672835715293</v>
       </c>
       <c r="C7" t="n">
-        <v>177.6835717485175</v>
+        <v>153.5492679350181</v>
       </c>
       <c r="D7" t="n">
         <v>34.61446055633404</v>
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.35038611942487</v>
+        <v>15.85522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>129.7625028088221</v>
+        <v>115.7431455921777</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>72.66405632982764</v>
+        <v>66.11874438561416</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>29.17656002251095</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>40.9977841293468</v>
+        <v>38.43542262126263</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.79680358741669</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.037126486312132</v>
+        <v>3.61675854244525</v>
       </c>
       <c r="C2" t="n">
-        <v>4.656429361242622</v>
+        <v>5.573381717009142</v>
       </c>
       <c r="D2" t="n">
-        <v>11.774100217032</v>
+        <v>11.76722798310227</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.16938468894497</v>
+        <v>23.12997591205485</v>
       </c>
       <c r="C3" t="n">
-        <v>39.1668246609265</v>
+        <v>32.40749171718721</v>
       </c>
       <c r="D3" t="n">
-        <v>78.7214396650305</v>
+        <v>83.03131208667399</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.79943003535994</v>
+        <v>49.41725244096745</v>
       </c>
       <c r="C4" t="n">
-        <v>142.3043297305751</v>
+        <v>92.2617040020025</v>
       </c>
       <c r="D4" t="n">
-        <v>152.4251668136555</v>
+        <v>162.6098174975119</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.5518496874405</v>
+        <v>49.30827844579606</v>
       </c>
       <c r="C5" t="n">
-        <v>276.7792215197821</v>
+        <v>210.167639786636</v>
       </c>
       <c r="D5" t="n">
-        <v>115.0608309377262</v>
+        <v>122.6939193382452</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.82647700272235</v>
+        <v>39.32586778901449</v>
       </c>
       <c r="C6" t="n">
-        <v>245.2130875851344</v>
+        <v>216.392901979265</v>
       </c>
       <c r="D6" t="n">
-        <v>53.41394734495622</v>
+        <v>54.09822549481625</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.144578954431539</v>
+        <v>10.4801567428347</v>
       </c>
       <c r="C7" t="n">
-        <v>177.9231181883537</v>
+        <v>157.8012172421111</v>
       </c>
       <c r="D7" t="n">
-        <v>34.19525428662065</v>
+        <v>34.55457394637499</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>90.37478491444013</v>
+        <v>82.69751786723006</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>31.28437234352885</v>
+        <v>29.28749751309084</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.19120412261664</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.036144738607885</v>
+        <v>4.52782041198629</v>
       </c>
       <c r="C2" t="n">
-        <v>5.779548734900973</v>
+        <v>7.950192908990671</v>
       </c>
       <c r="D2" t="n">
-        <v>11.75152001983432</v>
+        <v>14.84991577443725</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.85460352878024</v>
+        <v>18.00034415736527</v>
       </c>
       <c r="C3" t="n">
-        <v>29.05482330718435</v>
+        <v>27.1011453757332</v>
       </c>
       <c r="D3" t="n">
-        <v>71.77066591896308</v>
+        <v>74.95643721924397</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.68081848959532</v>
+        <v>46.82642024946012</v>
       </c>
       <c r="C4" t="n">
-        <v>121.4628077171196</v>
+        <v>86.64610713371074</v>
       </c>
       <c r="D4" t="n">
-        <v>155.3095415687327</v>
+        <v>165.8387856967797</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.98229715025711</v>
+        <v>59.76389149602459</v>
       </c>
       <c r="C5" t="n">
-        <v>272.3613568506714</v>
+        <v>193.3306666588032</v>
       </c>
       <c r="D5" t="n">
-        <v>135.4811831860599</v>
+        <v>146.3049516253809</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.15227837181205</v>
+        <v>50.03280825153021</v>
       </c>
       <c r="C6" t="n">
-        <v>327.6484788153306</v>
+        <v>269.4848360772282</v>
       </c>
       <c r="D6" t="n">
-        <v>69.59511300635215</v>
+        <v>73.13725872327464</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.28915790886308</v>
+        <v>21.67895280517807</v>
       </c>
       <c r="C7" t="n">
-        <v>250.9248957284423</v>
+        <v>225.1736534460484</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>40.36357511240336</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>144.5328970192154</v>
+        <v>132.6832022289564</v>
       </c>
       <c r="D8" t="n">
-        <v>32.62838495064274</v>
+        <v>33.04562772494764</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>58.242182554442</v>
+        <v>55.35780779936488</v>
       </c>
       <c r="D9" t="n">
         <v>32.39374724932775</v>
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>24.20008090968388</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
         <v>14.13520344574558</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.433351648200343</v>
+        <v>3.303581024790517</v>
       </c>
       <c r="C2" t="n">
-        <v>3.692353115672254</v>
+        <v>4.151811041259761</v>
       </c>
       <c r="D2" t="n">
-        <v>10.04327901444487</v>
+        <v>11.21352227790707</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.954921721062657</v>
+        <v>17.04314014572463</v>
       </c>
       <c r="C3" t="n">
-        <v>26.72317250959818</v>
+        <v>29.33953014141593</v>
       </c>
       <c r="D3" t="n">
-        <v>66.52322443976388</v>
+        <v>71.51050277733766</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.29869764846506</v>
+        <v>42.67853619901734</v>
       </c>
       <c r="C4" t="n">
-        <v>105.2413903998496</v>
+        <v>80.96669666464295</v>
       </c>
       <c r="D4" t="n">
-        <v>157.4664412749629</v>
+        <v>166.0047010587974</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.59021996336414</v>
+        <v>65.4580281806561</v>
       </c>
       <c r="C5" t="n">
-        <v>261.8812001078367</v>
+        <v>185.6484908730719</v>
       </c>
       <c r="D5" t="n">
-        <v>148.3175344190869</v>
+        <v>161.4729536559942</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.98247707670636</v>
+        <v>58.28439770572465</v>
       </c>
       <c r="C6" t="n">
-        <v>374.7831678439242</v>
+        <v>295.044637557294</v>
       </c>
       <c r="D6" t="n">
-        <v>81.8316163920844</v>
+        <v>88.79515285830703</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.49255961009142</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="C7" t="n">
-        <v>319.0159712518883</v>
+        <v>281.8263864673148</v>
       </c>
       <c r="D7" t="n">
-        <v>44.6155244194963</v>
+        <v>45.15450390912779</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>186.3406230045658</v>
+        <v>172.9888542268092</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>62.23593221531803</v>
+        <v>63.6781195928566</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.431789063419349</v>
+        <v>4.733005682173872</v>
       </c>
       <c r="C2" t="n">
-        <v>6.603235058764047</v>
+        <v>11.70635962543897</v>
       </c>
       <c r="D2" t="n">
-        <v>20.11011997379167</v>
+        <v>16.55422978900972</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.628179661997716</v>
+        <v>14.19116306488765</v>
       </c>
       <c r="C3" t="n">
-        <v>21.1910241961674</v>
+        <v>23.1937895128309</v>
       </c>
       <c r="D3" t="n">
-        <v>60.54438092090079</v>
+        <v>65.76236996897259</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.07874510498477</v>
+        <v>37.57344813693393</v>
       </c>
       <c r="C4" t="n">
-        <v>88.96892220195869</v>
+        <v>77.34208414056373</v>
       </c>
       <c r="D4" t="n">
-        <v>154.7607446020587</v>
+        <v>162.0354950905275</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.02571503342222</v>
+        <v>65.40894079544375</v>
       </c>
       <c r="C5" t="n">
-        <v>234.1468274628643</v>
+        <v>169.9896149903352</v>
       </c>
       <c r="D5" t="n">
-        <v>163.0682936753952</v>
+        <v>177.745421853885</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.86551023118075</v>
+        <v>69.03158982411449</v>
       </c>
       <c r="C6" t="n">
-        <v>391.2863467523131</v>
+        <v>296.1314322658952</v>
       </c>
       <c r="D6" t="n">
-        <v>99.38133835320039</v>
+        <v>109.6052589452267</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.27214940272139</v>
+        <v>35.2133266559246</v>
       </c>
       <c r="C7" t="n">
-        <v>400.7013072360399</v>
+        <v>338.6587793184585</v>
       </c>
       <c r="D7" t="n">
-        <v>51.98157744446011</v>
+        <v>54.91602133245383</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.260024272905162</v>
+        <v>9.763480918734528</v>
       </c>
       <c r="C8" t="n">
-        <v>271.5415975176253</v>
+        <v>249.9284218086317</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>116.7062400900438</v>
+        <v>116.3734276183041</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>43.98720588877834</v>
+        <v>45.26838664282043</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.079963532400496</v>
+        <v>7.813729978100364</v>
       </c>
       <c r="C2" t="n">
-        <v>7.530004891573035</v>
+        <v>4.103705403751667</v>
       </c>
       <c r="D2" t="n">
-        <v>10.51549966018759</v>
+        <v>7.548658097953725</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.795616551067416</v>
+        <v>3.422372497004381</v>
       </c>
       <c r="C2" t="n">
-        <v>3.962333734340127</v>
+        <v>6.835909264670541</v>
       </c>
       <c r="D2" t="n">
-        <v>15.12185988851362</v>
+        <v>12.31602494977624</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.56360529769568</v>
+        <v>18.78574232076272</v>
       </c>
       <c r="C3" t="n">
-        <v>26.1783025337412</v>
+        <v>32.90327430783185</v>
       </c>
       <c r="D3" t="n">
-        <v>67.51969835957439</v>
+        <v>71.95228924424873</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.40378571054848</v>
+        <v>50.32340557198725</v>
       </c>
       <c r="C4" t="n">
-        <v>129.4777959745906</v>
+        <v>108.3044432370996</v>
       </c>
       <c r="D4" t="n">
-        <v>157.8493228796191</v>
+        <v>166.8470405890412</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.51347941151687</v>
+        <v>40.07985002587604</v>
       </c>
       <c r="C5" t="n">
-        <v>337.9175598017522</v>
+        <v>251.0328879759095</v>
       </c>
       <c r="D5" t="n">
-        <v>146.1086020845316</v>
+        <v>161.3747788855695</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.65789413503238</v>
+        <v>21.85664913964674</v>
       </c>
       <c r="C6" t="n">
-        <v>329.0975384267988</v>
+        <v>278.179193746038</v>
       </c>
       <c r="D6" t="n">
-        <v>77.8467024605466</v>
+        <v>84.08570912103508</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.790928796724434</v>
+        <v>6.467753875577986</v>
       </c>
       <c r="C7" t="n">
-        <v>190.9185125494687</v>
+        <v>175.7672002298277</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>85.95201150680825</v>
+        <v>85.78511439708629</v>
       </c>
       <c r="D8" t="n">
-        <v>24.45042657426681</v>
+        <v>24.28352946454485</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>33.50312215512664</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>19.63593583264045</v>
+        <v>19.96874830438012</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.4988920646734</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.74879576089983</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.19741340401162</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
         <v>13.0179745583127</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
         <v>9.105709956889166</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.630723994482958</v>
+        <v>8.88579847113788</v>
       </c>
       <c r="C2" t="n">
-        <v>8.009097771245479</v>
+        <v>8.412596077690917</v>
       </c>
       <c r="D2" t="n">
-        <v>22.01078352921349</v>
+        <v>14.66731070144735</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.91489104936679</v>
+        <v>16.5915362017711</v>
       </c>
       <c r="C3" t="n">
-        <v>18.97227438456961</v>
+        <v>10.33780332571891</v>
       </c>
       <c r="D3" t="n">
-        <v>11.96750451476862</v>
+        <v>9.478774084502955</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39786025085413</v>
+        <v>13.39866058839303</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14173896035399</v>
+        <v>70.14592896276351</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576218853041663</v>
+        <v>1.57631301039918</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.500331476267379</v>
+        <v>5.573381717009142</v>
       </c>
       <c r="C2" t="n">
-        <v>5.471279955767474</v>
+        <v>6.243915399009714</v>
       </c>
       <c r="D2" t="n">
-        <v>30.39785416659399</v>
+        <v>28.18695833663017</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.91827826083604</v>
+        <v>25.04929267385737</v>
       </c>
       <c r="C3" t="n">
-        <v>26.64463269325843</v>
+        <v>24.39643045053324</v>
       </c>
       <c r="D3" t="n">
-        <v>27.5625667967292</v>
+        <v>19.50732688338412</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.02172162268045</v>
+        <v>19.16960567312322</v>
       </c>
       <c r="C4" t="n">
-        <v>29.46912083837651</v>
+        <v>16.2979936382013</v>
       </c>
       <c r="D4" t="n">
-        <v>21.33926809950867</v>
+        <v>20.0374706436774</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43877004918423</v>
+        <v>15.44194829590649</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13208553755412</v>
+        <v>86.14981680874151</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250267378775627</v>
+        <v>3.250936483348736</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.239587497565227</v>
+        <v>5.651921533348887</v>
       </c>
       <c r="C2" t="n">
-        <v>6.735770998837365</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="D2" t="n">
-        <v>30.56867826713293</v>
+        <v>28.50111760198915</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.03823140720339</v>
+        <v>21.80461651132166</v>
       </c>
       <c r="C3" t="n">
-        <v>23.43431770037137</v>
+        <v>24.33752558827843</v>
       </c>
       <c r="D3" t="n">
-        <v>45.48437113775472</v>
+        <v>37.52730599483433</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.31222113214627</v>
+        <v>35.83771819582557</v>
       </c>
       <c r="C4" t="n">
-        <v>50.73181261695392</v>
+        <v>42.65301075870693</v>
       </c>
       <c r="D4" t="n">
-        <v>30.3497485290859</v>
+        <v>25.30847406777853</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.08178815908875</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="C5" t="n">
-        <v>33.35487825178539</v>
+        <v>19.46314823669302</v>
       </c>
       <c r="D5" t="n">
-        <v>30.33600406122645</v>
+        <v>29.64878066825368</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.78845088416398</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5336,7 +5336,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72755501600167</v>
+        <v>16.73366213514132</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0380855976102</v>
+        <v>102.075339024362</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181888754000417</v>
+        <v>4.183415533785329</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.799764526062656</v>
+        <v>5.850234569606743</v>
       </c>
       <c r="C2" t="n">
-        <v>12.99637610881928</v>
+        <v>4.717297718905924</v>
       </c>
       <c r="D2" t="n">
-        <v>24.81072798172539</v>
+        <v>32.9209457665083</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.47510913559323</v>
+        <v>20.43016972537612</v>
       </c>
       <c r="C3" t="n">
-        <v>24.94130042639022</v>
+        <v>25.70215489718149</v>
       </c>
       <c r="D3" t="n">
-        <v>58.60052046649211</v>
+        <v>50.83980486442108</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.15830772675777</v>
+        <v>39.00287279431728</v>
       </c>
       <c r="C4" t="n">
-        <v>54.57339138367169</v>
+        <v>52.85042416271855</v>
       </c>
       <c r="D4" t="n">
-        <v>45.4608091928528</v>
+        <v>37.71383805864122</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.02260555939346</v>
+        <v>34.82749980815561</v>
       </c>
       <c r="C5" t="n">
-        <v>65.92435834017333</v>
+        <v>51.46812339513905</v>
       </c>
       <c r="D5" t="n">
-        <v>33.94392687433348</v>
+        <v>31.73499453977815</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.7132318593687</v>
+        <v>14.00757624419349</v>
       </c>
       <c r="C6" t="n">
-        <v>33.2881194078966</v>
+        <v>21.81639748377262</v>
       </c>
       <c r="D6" t="n">
-        <v>38.31957639216151</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04571873040065</v>
+        <v>18.05610099686825</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7268317173757</v>
+        <v>117.7945636462357</v>
       </c>
       <c r="D21" t="n">
-        <v>6.015239576800216</v>
+        <v>6.018700332289415</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.229770020522759</v>
+        <v>6.989061906533043</v>
       </c>
       <c r="C2" t="n">
-        <v>10.60483870127405</v>
+        <v>12.58207857762712</v>
       </c>
       <c r="D2" t="n">
-        <v>25.47831642061323</v>
+        <v>36.01639627799848</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.96183501272139</v>
+        <v>17.98070920328033</v>
       </c>
       <c r="C3" t="n">
-        <v>36.8891699870739</v>
+        <v>20.17000658375072</v>
       </c>
       <c r="D3" t="n">
-        <v>60.61310326019807</v>
+        <v>60.72600424618645</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.15157436154828</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="C4" t="n">
-        <v>48.77911643320702</v>
+        <v>49.59593052314037</v>
       </c>
       <c r="D4" t="n">
-        <v>55.49230723484671</v>
+        <v>46.96681017116741</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.01569226773472</v>
+        <v>28.44613973055134</v>
       </c>
       <c r="C5" t="n">
-        <v>62.88094045700822</v>
+        <v>56.6222988424348</v>
       </c>
       <c r="D5" t="n">
-        <v>33.87029579651497</v>
+        <v>30.38509144643879</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.16229147083699</v>
+        <v>16.58368222013712</v>
       </c>
       <c r="C6" t="n">
-        <v>47.2956956520901</v>
+        <v>35.34095385747668</v>
       </c>
       <c r="D6" t="n">
-        <v>31.396291581813</v>
+        <v>30.83276839957533</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>22.0382724649324</v>
+        <v>17.0676838383308</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.06405994715006</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.049542824687475</v>
+        <v>7.055161324171526</v>
       </c>
       <c r="C21" t="n">
-        <v>66.08946398144506</v>
+        <v>66.14213741410805</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405964265429671</v>
+        <v>4.409475827607204</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.422773407631881</v>
+        <v>5.934664872171968</v>
       </c>
       <c r="C2" t="n">
-        <v>10.04720600526186</v>
+        <v>6.957645979997145</v>
       </c>
       <c r="D2" t="n">
-        <v>26.65150492718816</v>
+        <v>26.7761868856275</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.99405276051229</v>
+        <v>21.88806506618264</v>
       </c>
       <c r="C3" t="n">
-        <v>39.75587328347459</v>
+        <v>38.86739161113123</v>
       </c>
       <c r="D3" t="n">
-        <v>67.36752746541613</v>
+        <v>76.30634031258334</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.09525488950772</v>
+        <v>32.65980087717864</v>
       </c>
       <c r="C4" t="n">
-        <v>75.81055772193871</v>
+        <v>50.28511741152163</v>
       </c>
       <c r="D4" t="n">
-        <v>74.38113306455534</v>
+        <v>67.4382133001219</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.32971266437347</v>
+        <v>37.33095645398497</v>
       </c>
       <c r="C5" t="n">
-        <v>78.76070957320037</v>
+        <v>78.12257356543995</v>
       </c>
       <c r="D5" t="n">
-        <v>46.48575379608648</v>
+        <v>41.52792788964008</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.78243722475149</v>
+        <v>29.22270216461057</v>
       </c>
       <c r="C6" t="n">
-        <v>78.32972233103602</v>
+        <v>67.46177524502383</v>
       </c>
       <c r="D6" t="n">
-        <v>35.58246379272141</v>
+        <v>34.01264921363075</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.31856928226148</v>
+        <v>13.83380690054181</v>
       </c>
       <c r="C7" t="n">
-        <v>48.98724694650735</v>
+        <v>36.89015173477814</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>25.11801501315464</v>
+        <v>21.27938148954961</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -6165,10 +6165,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
         <v>31.50624732468863</v>
@@ -6185,7 +6185,7 @@
         <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6255,7 +6255,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.2674545783539</v>
+        <v>7.274813389246527</v>
       </c>
       <c r="C21" t="n">
-        <v>75.39984125042172</v>
+        <v>75.47618891343274</v>
       </c>
       <c r="D21" t="n">
-        <v>5.450590933765425</v>
+        <v>5.456110041934895</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.549418861479719</v>
+        <v>5.804092427507142</v>
       </c>
       <c r="C2" t="n">
-        <v>11.2959890850638</v>
+        <v>9.433613690107601</v>
       </c>
       <c r="D2" t="n">
-        <v>28.95763028446392</v>
+        <v>29.91287080069607</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.01721379478671</v>
+        <v>21.08794068722149</v>
       </c>
       <c r="C3" t="n">
-        <v>39.31408681656352</v>
+        <v>31.80862561759665</v>
       </c>
       <c r="D3" t="n">
-        <v>72.6395126372215</v>
+        <v>80.02225537315752</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.52842661125882</v>
+        <v>38.02014334236623</v>
       </c>
       <c r="C4" t="n">
-        <v>88.57327787714723</v>
+        <v>77.49523678242623</v>
       </c>
       <c r="D4" t="n">
-        <v>89.78573629189205</v>
+        <v>90.52597406089413</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.31837366027901</v>
+        <v>44.10501561328796</v>
       </c>
       <c r="C5" t="n">
-        <v>113.1464229144449</v>
+        <v>85.73111827335273</v>
       </c>
       <c r="D5" t="n">
-        <v>62.66004722355269</v>
+        <v>56.32777453116076</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.95981476405067</v>
+        <v>40.57366912111219</v>
       </c>
       <c r="C6" t="n">
-        <v>103.7687688434794</v>
+        <v>98.69706020334036</v>
       </c>
       <c r="D6" t="n">
-        <v>41.74096714146165</v>
+        <v>39.08435785376978</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>25.03260296288517</v>
       </c>
       <c r="C7" t="n">
-        <v>82.88306818333271</v>
+        <v>69.82778721225863</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>46.64774216728719</v>
+        <v>36.30012136452581</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>28.06718511671205</v>
+        <v>25.4046853427947</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.470905642054171</v>
+        <v>7.481122203655703</v>
       </c>
       <c r="C21" t="n">
-        <v>84.04768847310943</v>
+        <v>84.16262479112666</v>
       </c>
       <c r="D21" t="n">
-        <v>6.5370424367974</v>
+        <v>6.545981928198739</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_80_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_80_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497638338651</v>
+        <v>10.84497647913004</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907212021524</v>
+        <v>37.78907245383138</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.972372195560848</v>
+        <v>1.360702318086079</v>
       </c>
       <c r="C2" t="n">
-        <v>7.803912501057896</v>
+        <v>2.651700549170635</v>
       </c>
       <c r="D2" t="n">
-        <v>28.02104297461246</v>
+        <v>15.29072049364407</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.27309009269663</v>
+        <v>11.33918598405066</v>
       </c>
       <c r="C3" t="n">
-        <v>34.34644343307466</v>
+        <v>33.35978699030662</v>
       </c>
       <c r="D3" t="n">
-        <v>84.52847733565038</v>
+        <v>66.01762437207677</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.01563551447249</v>
+        <v>20.54797944988574</v>
       </c>
       <c r="C4" t="n">
-        <v>77.78877934599602</v>
+        <v>133.1406966591354</v>
       </c>
       <c r="D4" t="n">
-        <v>107.2068493037517</v>
+        <v>75.45320155759286</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.41274461307373</v>
+        <v>21.23029410433728</v>
       </c>
       <c r="C5" t="n">
-        <v>115.5271610972434</v>
+        <v>156.2206034382737</v>
       </c>
       <c r="D5" t="n">
-        <v>74.95643721924398</v>
+        <v>45.57763716965817</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.55607977789376</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="C6" t="n">
-        <v>117.7763450876729</v>
+        <v>73.33851700264525</v>
       </c>
       <c r="D6" t="n">
-        <v>47.21519234034186</v>
+        <v>29.78622534684823</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.4110588551057</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>105.3405469179785</v>
+        <v>32.63820242768521</v>
       </c>
       <c r="D7" t="n">
-        <v>38.5669768136317</v>
+        <v>28.92523261022377</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.85937339858123</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>64.33883579781471</v>
+        <v>27.28767743954009</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.431249284071605</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>35.16718451382499</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>37.72365553568369</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.85539932116455</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.671834226611586</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.02098999766548</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.671834226611586</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.606581212504286</v>
+        <v>1.143736075447534</v>
       </c>
       <c r="C2" t="n">
-        <v>7.177557465748431</v>
+        <v>8.61189086165302</v>
       </c>
       <c r="D2" t="n">
-        <v>30.64819983117692</v>
+        <v>15.02172162268045</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.79479903427919</v>
+        <v>7.868707849538186</v>
       </c>
       <c r="C3" t="n">
-        <v>32.10805866739193</v>
+        <v>20.02765316663493</v>
       </c>
       <c r="D3" t="n">
-        <v>86.40361545076178</v>
+        <v>62.95457153482671</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.23710958500477</v>
+        <v>21.45413258090555</v>
       </c>
       <c r="C4" t="n">
-        <v>81.57930723209294</v>
+        <v>106.6963404975434</v>
       </c>
       <c r="D4" t="n">
-        <v>122.3179099675186</v>
+        <v>90.70465214306705</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.79977419272522</v>
+        <v>26.08994524035899</v>
       </c>
       <c r="C5" t="n">
-        <v>127.3817646260237</v>
+        <v>203.7371923238194</v>
       </c>
       <c r="D5" t="n">
-        <v>92.08793465835082</v>
+        <v>61.38377520803183</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.44540432922113</v>
+        <v>21.09186767803848</v>
       </c>
       <c r="C6" t="n">
-        <v>148.2871002402553</v>
+        <v>162.7776963549382</v>
       </c>
       <c r="D6" t="n">
-        <v>58.20389439397641</v>
+        <v>36.70951015719674</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.54996830749001</v>
+        <v>11.13890945238431</v>
       </c>
       <c r="C7" t="n">
-        <v>134.3855527481204</v>
+        <v>68.86960145291374</v>
       </c>
       <c r="D7" t="n">
-        <v>42.39971985101125</v>
+        <v>31.32069700858599</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.87181732356695</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>99.05343461998193</v>
+        <v>35.549084370777</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.09062388842696</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>55.02499532762521</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>35.44600086183109</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>38.57777603837842</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.846508389374458</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.0237955131961</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.827321938046266</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.491135894030663</v>
+        <v>0.6175193059712437</v>
       </c>
       <c r="C2" t="n">
-        <v>7.297330685666541</v>
+        <v>3.695298358784994</v>
       </c>
       <c r="D2" t="n">
-        <v>25.50973234714912</v>
+        <v>10.27398972494287</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.95326132529043</v>
+        <v>7.004769869800993</v>
       </c>
       <c r="C3" t="n">
-        <v>29.88930885579414</v>
+        <v>27.91599597025805</v>
       </c>
       <c r="D3" t="n">
-        <v>88.89234588102744</v>
+        <v>62.79749190214723</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.70933023074748</v>
+        <v>23.41959148480766</v>
       </c>
       <c r="C4" t="n">
-        <v>79.89462817160542</v>
+        <v>94.26545106637023</v>
       </c>
       <c r="D4" t="n">
-        <v>132.1579672071844</v>
+        <v>99.99591241605887</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.34602682691395</v>
+        <v>26.53173170727006</v>
       </c>
       <c r="C5" t="n">
-        <v>136.9047173572177</v>
+        <v>230.1707492606647</v>
       </c>
       <c r="D5" t="n">
-        <v>109.8821117978243</v>
+        <v>69.26230053461248</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.87937787222722</v>
+        <v>16.06041069377357</v>
       </c>
       <c r="C6" t="n">
-        <v>169.3789679182937</v>
+        <v>202.6670873261903</v>
       </c>
       <c r="D6" t="n">
-        <v>69.31335141523331</v>
+        <v>37.47429161880501</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>56.35329997147116</v>
+        <v>4.371722527011046</v>
       </c>
       <c r="C7" t="n">
-        <v>166.7842087359694</v>
+        <v>64.79731197569798</v>
       </c>
       <c r="D7" t="n">
-        <v>48.02906118716245</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>37.30150402285756</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>132.6832022289564</v>
+        <v>37.1346069131356</v>
       </c>
       <c r="D8" t="n">
-        <v>39.97185777840888</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.97031088916111</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>82.20468051969816</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>47.40368789955724</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.7169632282032</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.004733532310823</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108.0639026861961</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.00591691538853</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.858890372495717</v>
+        <v>0.9876381904722912</v>
       </c>
       <c r="C2" t="n">
-        <v>5.019676011813941</v>
+        <v>10.63723637551419</v>
       </c>
       <c r="D2" t="n">
-        <v>21.26072828316892</v>
+        <v>11.28518986031708</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.95879195861741</v>
+        <v>4.486587008407923</v>
       </c>
       <c r="C3" t="n">
-        <v>45.75926049494383</v>
+        <v>20.57743188101315</v>
       </c>
       <c r="D3" t="n">
-        <v>96.68251391422589</v>
+        <v>56.82846586032662</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.58474608329938</v>
+        <v>18.8377749490878</v>
       </c>
       <c r="C4" t="n">
-        <v>111.2909197534184</v>
+        <v>82.16639235923255</v>
       </c>
       <c r="D4" t="n">
-        <v>125.7638444094249</v>
+        <v>107.8832734719777</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.9810533606456</v>
+        <v>30.87596529856219</v>
       </c>
       <c r="C5" t="n">
-        <v>101.19364461524</v>
+        <v>204.1053477129119</v>
       </c>
       <c r="D5" t="n">
-        <v>70.93127163183206</v>
+        <v>87.89096322269572</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.97868895460962</v>
+        <v>24.43275511559037</v>
       </c>
       <c r="C6" t="n">
-        <v>109.8467688804714</v>
+        <v>281.5200811835899</v>
       </c>
       <c r="D6" t="n">
-        <v>31.5975498611836</v>
+        <v>47.93972214607601</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.73316991308989</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>93.30333831620835</v>
+        <v>168.1017141550686</v>
       </c>
       <c r="D7" t="n">
-        <v>28.086820070797</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.18487166803466</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>60.58365082907067</v>
+        <v>58.66433406726815</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>36.16562192904399</v>
+        <v>35.27812200440487</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>27.90126975469435</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>32.02951885105219</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>31.62994753542373</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>30.59224021203486</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
+        <v>23.65030219530566</v>
+      </c>
+      <c r="D15" t="n">
         <v>17.5585576904542</v>
-      </c>
-      <c r="D15" t="n">
-        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>47.22206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.845906668162256</v>
+        <v>0.5664684253504096</v>
       </c>
       <c r="C2" t="n">
-        <v>2.18831563276614</v>
+        <v>4.683918296961532</v>
       </c>
       <c r="D2" t="n">
-        <v>15.63433219013046</v>
+        <v>8.22115527536279</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.72946390645116</v>
+        <v>4.059526757060561</v>
       </c>
       <c r="C3" t="n">
-        <v>33.07998889459628</v>
+        <v>31.51410130632262</v>
       </c>
       <c r="D3" t="n">
-        <v>93.34948045830797</v>
+        <v>53.59360717483338</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.50963453615788</v>
+        <v>15.2514505854742</v>
       </c>
       <c r="C4" t="n">
-        <v>116.7788894201581</v>
+        <v>70.15667269318131</v>
       </c>
       <c r="D4" t="n">
-        <v>141.2322612375376</v>
+        <v>111.3802587945049</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.3680829402971</v>
+        <v>31.98043146583985</v>
       </c>
       <c r="C5" t="n">
-        <v>149.4220005863646</v>
+        <v>187.5874425889593</v>
       </c>
       <c r="D5" t="n">
-        <v>91.4497986505904</v>
+        <v>101.8072369303943</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.21769561509809</v>
+        <v>29.66547037922588</v>
       </c>
       <c r="C6" t="n">
-        <v>134.3197756519359</v>
+        <v>314.284929065123</v>
       </c>
       <c r="D6" t="n">
-        <v>40.25165587411923</v>
+        <v>57.51961624411638</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.05634483423634</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C7" t="n">
-        <v>120.0127663579471</v>
+        <v>248.3497715002029</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>40.06414206260808</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>80.02716411167874</v>
+        <v>96.96722074845746</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
+        <v>44.26405874137593</v>
+      </c>
+      <c r="D9" t="n">
         <v>41.04687151455913</v>
-      </c>
-      <c r="D9" t="n">
-        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.039711876526377</v>
+        <v>1.723948968657399</v>
       </c>
       <c r="C2" t="n">
-        <v>11.78489944177871</v>
+        <v>10.55967830687869</v>
       </c>
       <c r="D2" t="n">
-        <v>16.86544381125595</v>
+        <v>12.41419972020092</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.07950586851076</v>
+        <v>3.013965452037708</v>
       </c>
       <c r="C3" t="n">
-        <v>20.34181243199391</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D3" t="n">
-        <v>85.00953371073132</v>
+        <v>48.47870163570749</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.98858854711009</v>
+        <v>11.69065166217102</v>
       </c>
       <c r="C4" t="n">
-        <v>99.57474265093698</v>
+        <v>74.11311594129596</v>
       </c>
       <c r="D4" t="n">
-        <v>153.4972353066931</v>
+        <v>112.2864119255247</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.97662764820988</v>
+        <v>28.74066404182538</v>
       </c>
       <c r="C5" t="n">
-        <v>180.9361018926872</v>
+        <v>160.4175748739288</v>
       </c>
       <c r="D5" t="n">
-        <v>116.3371029532471</v>
+        <v>113.9072773852362</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.77242412572655</v>
+        <v>35.38120551335081</v>
       </c>
       <c r="C6" t="n">
-        <v>183.2255375389907</v>
+        <v>311.6283197774311</v>
       </c>
       <c r="D6" t="n">
-        <v>55.50703345041042</v>
+        <v>72.49323222928874</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.41672835715293</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="C7" t="n">
-        <v>153.5492679350181</v>
+        <v>336.3232015300553</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>45.87314322863646</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.85522542358599</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>115.7431455921777</v>
+        <v>193.0165073934442</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>41.39048321104552</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>66.11874438561416</v>
+        <v>74.43905617910588</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>38.43542262126263</v>
+        <v>40.42837046088366</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.58460721457913</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.96708790860789</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.61675854244525</v>
+        <v>1.185951226730147</v>
       </c>
       <c r="C2" t="n">
-        <v>5.573381717009142</v>
+        <v>5.745187565252335</v>
       </c>
       <c r="D2" t="n">
-        <v>11.76722798310227</v>
+        <v>9.037969365296137</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.12997591205485</v>
+        <v>4.869468613064179</v>
       </c>
       <c r="C3" t="n">
-        <v>32.40749171718721</v>
+        <v>34.08137155292803</v>
       </c>
       <c r="D3" t="n">
-        <v>83.03131208667399</v>
+        <v>53.4954324044087</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.41725244096745</v>
+        <v>19.5907754382451</v>
       </c>
       <c r="C4" t="n">
-        <v>92.2617040020025</v>
+        <v>103.0717279734641</v>
       </c>
       <c r="D4" t="n">
-        <v>162.6098174975119</v>
+        <v>114.9665831581185</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.30827844579606</v>
+        <v>21.25483779694345</v>
       </c>
       <c r="C5" t="n">
-        <v>210.167639786636</v>
+        <v>252.7264027657352</v>
       </c>
       <c r="D5" t="n">
-        <v>122.6939193382452</v>
+        <v>104.3106935762236</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.32586778901449</v>
+        <v>12.03524510636165</v>
       </c>
       <c r="C6" t="n">
-        <v>216.392901979265</v>
+        <v>291.7440017756162</v>
       </c>
       <c r="D6" t="n">
-        <v>54.09822549481625</v>
+        <v>62.18880832551422</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.4801567428347</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>157.8012172421111</v>
+        <v>135.7030581672196</v>
       </c>
       <c r="D7" t="n">
-        <v>34.55457394637499</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>82.69751786723006</v>
+        <v>54.82570054366312</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>29.28749751309084</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>26.29218526743382</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>34.04210164475815</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.52782041198629</v>
+        <v>0.5969026041820606</v>
       </c>
       <c r="C2" t="n">
-        <v>7.950192908990671</v>
+        <v>2.926589906359742</v>
       </c>
       <c r="D2" t="n">
-        <v>14.84991577443725</v>
+        <v>6.642504966933919</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.00034415736527</v>
+        <v>4.481678269886689</v>
       </c>
       <c r="C3" t="n">
-        <v>27.1011453757332</v>
+        <v>27.87672606208818</v>
       </c>
       <c r="D3" t="n">
-        <v>74.95643721924397</v>
+        <v>48.60632883725958</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.82642024946012</v>
+        <v>13.68163600638355</v>
       </c>
       <c r="C4" t="n">
-        <v>86.64610713371074</v>
+        <v>90.93438110586081</v>
       </c>
       <c r="D4" t="n">
-        <v>165.8387856967797</v>
+        <v>110.6017328650372</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.76389149602459</v>
+        <v>19.85584731839174</v>
       </c>
       <c r="C5" t="n">
-        <v>193.3306666588032</v>
+        <v>200.0310947402877</v>
       </c>
       <c r="D5" t="n">
-        <v>146.3049516253809</v>
+        <v>107.0841308407209</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.03280825153021</v>
+        <v>11.83398682699105</v>
       </c>
       <c r="C6" t="n">
-        <v>269.4848360772282</v>
+        <v>283.6534189449182</v>
       </c>
       <c r="D6" t="n">
-        <v>73.13725872327464</v>
+        <v>65.24793417194728</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.67895280517807</v>
+        <v>3.653083207502381</v>
       </c>
       <c r="C7" t="n">
-        <v>225.1736534460484</v>
+        <v>183.3727996946277</v>
       </c>
       <c r="D7" t="n">
-        <v>40.36357511240336</v>
+        <v>34.13536767666159</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>132.6832022289564</v>
+        <v>66.00780689503429</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>26.70353755551324</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>55.35780779936488</v>
+        <v>28.28906009787183</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>20.63437324785945</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>17.36711688812608</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>13.14952875068177</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.303581024790517</v>
+        <v>0.7107853378746907</v>
       </c>
       <c r="C2" t="n">
-        <v>4.151811041259761</v>
+        <v>8.44008501340983</v>
       </c>
       <c r="D2" t="n">
-        <v>11.21352227790707</v>
+        <v>13.36944023643306</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.04314014572463</v>
+        <v>3.180862561759666</v>
       </c>
       <c r="C3" t="n">
-        <v>29.33953014141593</v>
+        <v>18.44703936279756</v>
       </c>
       <c r="D3" t="n">
-        <v>71.51050277733766</v>
+        <v>42.84346981333081</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.67853619901734</v>
+        <v>11.20566829627309</v>
       </c>
       <c r="C4" t="n">
-        <v>80.96669666464295</v>
+        <v>79.11610224213771</v>
       </c>
       <c r="D4" t="n">
-        <v>166.0047010587974</v>
+        <v>110.1167494991392</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.4580281806561</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="C5" t="n">
-        <v>185.6484908730719</v>
+        <v>184.7403742466436</v>
       </c>
       <c r="D5" t="n">
-        <v>161.4729536559942</v>
+        <v>122.0557833304847</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.28439770572465</v>
+        <v>19.07928488433252</v>
       </c>
       <c r="C6" t="n">
-        <v>295.044637557294</v>
+        <v>302.3704389263837</v>
       </c>
       <c r="D6" t="n">
-        <v>88.79515285830703</v>
+        <v>82.35488791844796</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.40326162673396</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>281.8263864673148</v>
+        <v>299.6725962351134</v>
       </c>
       <c r="D7" t="n">
-        <v>45.15450390912779</v>
+        <v>43.59745205019235</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>172.9888542268092</v>
+        <v>152.0432669567035</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>63.6781195928566</v>
+        <v>53.58280795008665</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>22.40937309713768</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.78359889890498</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>16.34806277111788</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>13.0179745583127</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.733005682173872</v>
+        <v>0.6175193059712437</v>
       </c>
       <c r="C2" t="n">
-        <v>11.70635962543897</v>
+        <v>9.382562809486767</v>
       </c>
       <c r="D2" t="n">
-        <v>16.55422978900972</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.19116306488765</v>
+        <v>2.763619787454771</v>
       </c>
       <c r="C3" t="n">
-        <v>23.1937895128309</v>
+        <v>25.89359569950962</v>
       </c>
       <c r="D3" t="n">
-        <v>65.76236996897259</v>
+        <v>43.22635141798706</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.57344813693393</v>
+        <v>8.589310664455343</v>
       </c>
       <c r="C4" t="n">
-        <v>77.34208414056373</v>
+        <v>62.2054980364864</v>
       </c>
       <c r="D4" t="n">
-        <v>162.0354950905275</v>
+        <v>105.9178145680756</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.40894079544375</v>
+        <v>19.04590546238812</v>
       </c>
       <c r="C5" t="n">
-        <v>169.9896149903352</v>
+        <v>165.5472066286184</v>
       </c>
       <c r="D5" t="n">
-        <v>177.745421853885</v>
+        <v>132.9777265402305</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>69.03158982411449</v>
+        <v>23.18495378349268</v>
       </c>
       <c r="C6" t="n">
-        <v>296.1314322658952</v>
+        <v>296.6949554481329</v>
       </c>
       <c r="D6" t="n">
-        <v>109.6052589452267</v>
+        <v>99.34108669732626</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.2133266559246</v>
+        <v>14.67221943996858</v>
       </c>
       <c r="C7" t="n">
-        <v>338.6587793184585</v>
+        <v>367.2246922689279</v>
       </c>
       <c r="D7" t="n">
-        <v>54.91602133245383</v>
+        <v>54.31715523286327</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>249.9284218086317</v>
+        <v>266.4512356711056</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>116.3734276183041</v>
+        <v>114.5984277690259</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>24.4062479275757</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>45.26838664282043</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1930287493049</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>21.67895280517806</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.813729978100364</v>
+        <v>6.461863389352506</v>
       </c>
       <c r="C2" t="n">
-        <v>4.103705403751667</v>
+        <v>3.4626241528785</v>
       </c>
       <c r="D2" t="n">
-        <v>7.548658097953725</v>
+        <v>7.485826244881929</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.422372497004381</v>
+        <v>0.4859651136021712</v>
       </c>
       <c r="C2" t="n">
-        <v>6.835909264670541</v>
+        <v>16.29701189049705</v>
       </c>
       <c r="D2" t="n">
-        <v>12.31602494977624</v>
+        <v>18.75923513274805</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.78574232076272</v>
+        <v>2.395464398362217</v>
       </c>
       <c r="C3" t="n">
-        <v>32.90327430783185</v>
+        <v>30.68452449623406</v>
       </c>
       <c r="D3" t="n">
-        <v>71.95228924424873</v>
+        <v>44.31609136970102</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.32340557198725</v>
+        <v>6.930157044278235</v>
       </c>
       <c r="C4" t="n">
-        <v>108.3044432370996</v>
+        <v>63.16270204812704</v>
       </c>
       <c r="D4" t="n">
-        <v>166.8470405890412</v>
+        <v>102.6122700478766</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.07985002587604</v>
+        <v>16.64062358698344</v>
       </c>
       <c r="C5" t="n">
-        <v>251.0328879759095</v>
+        <v>141.1016887928728</v>
       </c>
       <c r="D5" t="n">
-        <v>161.3747788855695</v>
+        <v>139.113649691773</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.85664913964674</v>
+        <v>24.23149683621978</v>
       </c>
       <c r="C6" t="n">
-        <v>278.179193746038</v>
+        <v>283.6131672890441</v>
       </c>
       <c r="D6" t="n">
-        <v>84.08570912103508</v>
+        <v>113.0266496945268</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.467753875577986</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="C7" t="n">
-        <v>175.7672002298277</v>
+        <v>396.8685641986604</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>66.53402366451058</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>85.78511439708629</v>
+        <v>357.4101604695725</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>203.6812327046772</v>
       </c>
       <c r="D9" t="n">
-        <v>19.96874830438012</v>
+        <v>26.73593522975338</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>78.57908624791472</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>22.06477965294707</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.45958109877452</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.88579847113788</v>
+        <v>5.825690877000572</v>
       </c>
       <c r="C2" t="n">
-        <v>8.412596077690917</v>
+        <v>13.82791641431632</v>
       </c>
       <c r="D2" t="n">
-        <v>14.66731070144735</v>
+        <v>17.2964310534203</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.5915362017711</v>
+        <v>10.66178006812036</v>
       </c>
       <c r="C3" t="n">
-        <v>10.33780332571891</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="D3" t="n">
-        <v>9.478774084502955</v>
+        <v>8.158323422290994</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39866058839303</v>
+        <v>11.67869551192989</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14592896276351</v>
+        <v>59.9506369612401</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57631301039918</v>
+        <v>0.7785797007953259</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.573381717009142</v>
+        <v>3.029673415305656</v>
       </c>
       <c r="C2" t="n">
-        <v>6.243915399009714</v>
+        <v>10.43205110532661</v>
       </c>
       <c r="D2" t="n">
-        <v>28.18695833663017</v>
+        <v>22.42802630351838</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.04929267385737</v>
+        <v>16.75843331149305</v>
       </c>
       <c r="C3" t="n">
-        <v>24.39643045053324</v>
+        <v>38.2439818189345</v>
       </c>
       <c r="D3" t="n">
-        <v>19.50732688338412</v>
+        <v>21.32846887476196</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.16960567312322</v>
+        <v>13.12007631955437</v>
       </c>
       <c r="C4" t="n">
-        <v>16.2979936382013</v>
+        <v>11.69065166217102</v>
       </c>
       <c r="D4" t="n">
-        <v>20.0374706436774</v>
+        <v>18.46765606458675</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44194829590649</v>
+        <v>13.63028717926866</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14981680874151</v>
+        <v>73.76390708780686</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250936483348736</v>
+        <v>1.603563197561019</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.651921533348887</v>
+        <v>2.731222113214627</v>
       </c>
       <c r="C2" t="n">
-        <v>6.886960145291375</v>
+        <v>10.82376843932108</v>
       </c>
       <c r="D2" t="n">
-        <v>28.50111760198915</v>
+        <v>24.96682586670063</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.80461651132166</v>
+        <v>13.15051049838602</v>
       </c>
       <c r="C3" t="n">
-        <v>24.33752558827843</v>
+        <v>39.81968688425063</v>
       </c>
       <c r="D3" t="n">
-        <v>37.52730599483433</v>
+        <v>35.01403187196249</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.83771819582557</v>
+        <v>24.88730430265664</v>
       </c>
       <c r="C4" t="n">
-        <v>42.65301075870693</v>
+        <v>63.66044813418017</v>
       </c>
       <c r="D4" t="n">
-        <v>25.30847406777853</v>
+        <v>25.35952494839936</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.27246819789088</v>
+        <v>11.90369091399258</v>
       </c>
       <c r="C5" t="n">
-        <v>19.46314823669302</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="D5" t="n">
-        <v>29.64878066825368</v>
+        <v>26.38446955163304</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.427682146153116</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.50568218314512</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.78845088416398</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73366213514132</v>
+        <v>14.84001740001755</v>
       </c>
       <c r="C21" t="n">
-        <v>102.075339024362</v>
+        <v>87.39121357788113</v>
       </c>
       <c r="D21" t="n">
-        <v>4.183415533785329</v>
+        <v>2.473336233336259</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.850234569606743</v>
+        <v>2.012582793705961</v>
       </c>
       <c r="C2" t="n">
-        <v>4.717297718905924</v>
+        <v>8.880889732616646</v>
       </c>
       <c r="D2" t="n">
-        <v>32.9209457665083</v>
+        <v>20.32610446872596</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.43016972537612</v>
+        <v>11.06429662686155</v>
       </c>
       <c r="C3" t="n">
-        <v>25.70215489718149</v>
+        <v>41.2137686242811</v>
       </c>
       <c r="D3" t="n">
-        <v>50.83980486442108</v>
+        <v>46.8637266622215</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.00287279431728</v>
+        <v>25.49991487010665</v>
       </c>
       <c r="C4" t="n">
-        <v>52.85042416271855</v>
+        <v>84.91037719260238</v>
       </c>
       <c r="D4" t="n">
-        <v>37.71383805864122</v>
+        <v>37.19056653227767</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.82749980815561</v>
+        <v>25.08365384350601</v>
       </c>
       <c r="C5" t="n">
-        <v>51.46812339513905</v>
+        <v>73.43472827766143</v>
       </c>
       <c r="D5" t="n">
-        <v>31.73499453977815</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.00757624419349</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="C6" t="n">
-        <v>21.81639748377262</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>33.73088762251191</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>35.15344004596554</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.13486895504285</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05610099686825</v>
+        <v>16.0786863211432</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7945636462357</v>
+        <v>100.7033511692653</v>
       </c>
       <c r="D21" t="n">
-        <v>6.018700332289415</v>
+        <v>3.384986593924884</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.989061906533043</v>
+        <v>2.80387144332889</v>
       </c>
       <c r="C2" t="n">
-        <v>12.58207857762712</v>
+        <v>8.408669086873932</v>
       </c>
       <c r="D2" t="n">
-        <v>36.01639627799848</v>
+        <v>25.25447794404495</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.98070920328033</v>
+        <v>8.791550691530187</v>
       </c>
       <c r="C3" t="n">
-        <v>20.17000658375072</v>
+        <v>37.34077393102744</v>
       </c>
       <c r="D3" t="n">
-        <v>60.72600424618645</v>
+        <v>51.88536616944393</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.63954402828795</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="C4" t="n">
-        <v>49.59593052314037</v>
+        <v>94.07401026404212</v>
       </c>
       <c r="D4" t="n">
-        <v>46.96681017116741</v>
+        <v>51.49757582626644</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.44613973055134</v>
+        <v>32.00497515844602</v>
       </c>
       <c r="C5" t="n">
-        <v>56.6222988424348</v>
+        <v>118.4724042099839</v>
       </c>
       <c r="D5" t="n">
-        <v>30.38509144643879</v>
+        <v>35.4901795085222</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.58368222013712</v>
+        <v>22.09815907489146</v>
       </c>
       <c r="C6" t="n">
-        <v>35.34095385747668</v>
+        <v>68.83033154474388</v>
       </c>
       <c r="D6" t="n">
-        <v>30.83276839957533</v>
+        <v>35.74347041621788</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.347980655659875</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>17.0676838383308</v>
+        <v>21.91849924501429</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.055161324171526</v>
+        <v>17.33970941246203</v>
       </c>
       <c r="C21" t="n">
-        <v>66.14213741410805</v>
+        <v>114.4420821222494</v>
       </c>
       <c r="D21" t="n">
-        <v>4.409475827607204</v>
+        <v>4.334927353115508</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.934664872171968</v>
+        <v>2.884374755077129</v>
       </c>
       <c r="C2" t="n">
-        <v>6.957645979997145</v>
+        <v>6.812347319768617</v>
       </c>
       <c r="D2" t="n">
-        <v>26.7761868856275</v>
+        <v>24.94817266031995</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.88806506618264</v>
+        <v>9.090983741325465</v>
       </c>
       <c r="C3" t="n">
-        <v>38.86739161113123</v>
+        <v>34.69496386808228</v>
       </c>
       <c r="D3" t="n">
-        <v>76.30634031258334</v>
+        <v>59.52336330848411</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.65980087717864</v>
+        <v>20.0374706436774</v>
       </c>
       <c r="C4" t="n">
-        <v>50.28511741152163</v>
+        <v>93.6145523384546</v>
       </c>
       <c r="D4" t="n">
-        <v>67.4382133001219</v>
+        <v>63.04783756673017</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.33095645398497</v>
+        <v>33.33033455917922</v>
       </c>
       <c r="C5" t="n">
-        <v>78.12257356543995</v>
+        <v>145.9613399288945</v>
       </c>
       <c r="D5" t="n">
-        <v>41.52792788964008</v>
+        <v>44.76769531365456</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.22270216461057</v>
+        <v>31.83905979642831</v>
       </c>
       <c r="C6" t="n">
-        <v>67.46177524502383</v>
+        <v>125.2631530802591</v>
       </c>
       <c r="D6" t="n">
-        <v>34.01264921363075</v>
+        <v>38.35982804803563</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.83380690054181</v>
+        <v>17.30723027816702</v>
       </c>
       <c r="C7" t="n">
-        <v>36.89015173477814</v>
+        <v>58.92842419971054</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>39.34550274309942</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>9.095892479846697</v>
       </c>
       <c r="C8" t="n">
-        <v>21.27938148954961</v>
+        <v>27.45457454926205</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>45.34594471145593</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.26022956155019</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.274813389246527</v>
+        <v>17.72824916914201</v>
       </c>
       <c r="C21" t="n">
-        <v>75.47618891343274</v>
+        <v>127.6433940178225</v>
       </c>
       <c r="D21" t="n">
-        <v>5.456110041934895</v>
+        <v>5.318474750742602</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.804092427507142</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C2" t="n">
-        <v>9.433613690107601</v>
+        <v>4.304963683122264</v>
       </c>
       <c r="D2" t="n">
-        <v>29.91287080069607</v>
+        <v>19.78712497909446</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.08794068722149</v>
+        <v>12.7578114166873</v>
       </c>
       <c r="C3" t="n">
-        <v>31.80862561759665</v>
+        <v>51.47303213366027</v>
       </c>
       <c r="D3" t="n">
-        <v>80.02225537315752</v>
+        <v>64.97697180557515</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.02014334236623</v>
+        <v>16.0044510746315</v>
       </c>
       <c r="C4" t="n">
-        <v>77.49523678242623</v>
+        <v>130.3711863854552</v>
       </c>
       <c r="D4" t="n">
-        <v>90.52597406089413</v>
+        <v>58.00656310542279</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.10501561328796</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="C5" t="n">
-        <v>85.73111827335273</v>
+        <v>74.83371875621313</v>
       </c>
       <c r="D5" t="n">
-        <v>56.32777453116076</v>
+        <v>35.80924751240241</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.57366912111219</v>
+        <v>10.74719211838983</v>
       </c>
       <c r="C6" t="n">
-        <v>98.69706020334036</v>
+        <v>38.80259626265094</v>
       </c>
       <c r="D6" t="n">
-        <v>39.08435785376978</v>
+        <v>25.88181472705867</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.03260296288517</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>69.82778721225863</v>
+        <v>19.28348840681585</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>26.76931465169778</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>36.30012136452581</v>
+        <v>22.94835258676919</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>25.4046853427947</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>96.83959354690535</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.481122203655703</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.16262479112666</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.545981928198739</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
